--- a/Bases/Lista de ações Tratada.xlsx
+++ b/Bases/Lista de ações Tratada.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D251"/>
+  <dimension ref="A1:D250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Volume no último dia útil (lido em 10/03/2025)</t>
+          <t>Volume no último dia útil (lido em 15/03/2025)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -453,55 +453,55 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>HAPV3</t>
+          <t>B3SA3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hapvida</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>97225000</v>
+        <v>126021900</v>
       </c>
       <c r="D2" t="n">
-        <v>15210568704</v>
+        <v>67275739136</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>B3SA3</t>
+          <t>HAPV3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>Hapvida</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>41638200</v>
+        <v>111755000</v>
       </c>
       <c r="D3" t="n">
-        <v>54814535680</v>
+        <v>16175141888</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>MGLU3</t>
+          <t>NTCO3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Magazine Luiza</t>
+          <t>Natura</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>40884800</v>
+        <v>105384100</v>
       </c>
       <c r="D4" t="n">
-        <v>6073303552</v>
+        <v>13171654656</v>
       </c>
     </row>
     <row r="5">
@@ -516,28 +516,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>36134200</v>
+        <v>102051600</v>
       </c>
       <c r="D5" t="n">
-        <v>3024730624</v>
+        <v>3164490240</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ABEV3</t>
+          <t>MGLU3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ambev</t>
+          <t>Magazine Luiza</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>30190400</v>
+        <v>65687600</v>
       </c>
       <c r="D6" t="n">
-        <v>205837058048</v>
+        <v>7071379456</v>
       </c>
     </row>
     <row r="7">
@@ -552,568 +552,568 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>29808500</v>
+        <v>42086800</v>
       </c>
       <c r="D7" t="n">
-        <v>117054726144</v>
+        <v>122790780928</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>PETR4</t>
+          <t>ABEV3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Petrobras</t>
+          <t>Ambev</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28074700</v>
+        <v>41765100</v>
       </c>
       <c r="D8" t="n">
-        <v>466964938752</v>
+        <v>213556019200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>LREN3</t>
+          <t>PETR4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lojas Renner</t>
+          <t>Petrobras</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26935300</v>
+        <v>41510300</v>
       </c>
       <c r="D9" t="n">
-        <v>12473517056</v>
+        <v>479207391232</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ITSA4</t>
+          <t>AMOB3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Itaúsa</t>
+          <t>Automob</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26623100</v>
+        <v>35798400</v>
       </c>
       <c r="D10" t="n">
-        <v>99187204096</v>
+        <v>530404000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>VALE3</t>
+          <t>ITSA4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vale</t>
+          <t>Itaúsa</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25480600</v>
+        <v>35728500</v>
       </c>
       <c r="D11" t="n">
-        <v>230471434240</v>
+        <v>102134104064</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>POMO4</t>
+          <t>CCRO3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Marcopolo</t>
+          <t>Grupo CCR</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24491700</v>
+        <v>32515300</v>
       </c>
       <c r="D12" t="n">
-        <v>7226331648</v>
+        <v>23500873728</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>CVCB3</t>
+          <t>VALE3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CVC</t>
+          <t>Vale</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24316300</v>
+        <v>31782000</v>
       </c>
       <c r="D13" t="n">
-        <v>955580096</v>
+        <v>240289628160</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ASAI3</t>
+          <t>ITUB4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Assaí</t>
+          <t>Itaú Unibanco</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22826700</v>
+        <v>31638000</v>
       </c>
       <c r="D14" t="n">
-        <v>9533329408</v>
+        <v>317260791808</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>ITUB4</t>
+          <t>CMIG4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Itaú Unibanco</t>
+          <t>Cemig</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20645900</v>
+        <v>28449400</v>
       </c>
       <c r="D15" t="n">
-        <v>304529473536</v>
+        <v>35083624448</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>AMOB3</t>
+          <t>LWSA3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vamos Locação</t>
+          <t>Locaweb</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16946700</v>
+        <v>27984300</v>
       </c>
       <c r="D16" t="n">
-        <v>473575008</v>
+        <v>1480759168</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>BBAS3</t>
+          <t>CSNA3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Banco do Brasil</t>
+          <t>Siderúrgica Nacional</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16830600</v>
+        <v>26742900</v>
       </c>
       <c r="D17" t="n">
-        <v>159651627008</v>
+        <v>13552640000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>BHIA3</t>
+          <t>AZEV4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Casas Bahia</t>
+          <t>Azevedo &amp; Travassos</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16304700</v>
+        <v>23465200</v>
       </c>
       <c r="D18" t="n">
-        <v>445877856</v>
+        <v>578351232</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>CSAN3</t>
+          <t>LREN3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cosan</t>
+          <t>Lojas Renner</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16276000</v>
+        <v>23036000</v>
       </c>
       <c r="D19" t="n">
-        <v>13177757696</v>
+        <v>12406659072</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>CPLE6</t>
+          <t>BBAS3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Copel</t>
+          <t>Banco do Brasil</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16106300</v>
+        <v>22864500</v>
       </c>
       <c r="D20" t="n">
-        <v>28001288192</v>
+        <v>159137906688</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>MRVE3</t>
+          <t>VAMO3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MRV</t>
+          <t>Grupo Vamos</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>15874700</v>
+        <v>20637800</v>
       </c>
       <c r="D21" t="n">
-        <v>2650905856</v>
+        <v>4228711936</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>RADL3</t>
+          <t>CSAN3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RaiaDrogasil</t>
+          <t>Cosan</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15847100</v>
+        <v>19310200</v>
       </c>
       <c r="D22" t="n">
-        <v>30526386176</v>
+        <v>13884040192</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>RAIZ4</t>
+          <t>USIM5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Raízen</t>
+          <t>Usiminas</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>14323600</v>
+        <v>18908100</v>
       </c>
       <c r="D23" t="n">
-        <v>18084849664</v>
+        <v>7217229824</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>BRAV3</t>
+          <t>ASAI3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3R Petroleum</t>
+          <t>Assaí</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>13702800</v>
+        <v>17930500</v>
       </c>
       <c r="D24" t="n">
-        <v>7798240256</v>
+        <v>10180571136</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>RENT3</t>
+          <t>CVCB3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Localiza</t>
+          <t>CVC</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>13520000</v>
+        <v>17711400</v>
       </c>
       <c r="D25" t="n">
-        <v>31349063680</v>
+        <v>1060047488</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>VAMO3</t>
+          <t>CPLE6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Grupo Vamos</t>
+          <t>Copel</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>13260500</v>
+        <v>16997000</v>
       </c>
       <c r="D26" t="n">
-        <v>4042725120</v>
+        <v>29502375936</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>LWSA3</t>
+          <t>PRIO3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Locaweb</t>
+          <t>PetroRio</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>12582100</v>
+        <v>16461300</v>
       </c>
       <c r="D27" t="n">
-        <v>1475092096</v>
+        <v>33118572544</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>AZUL4</t>
+          <t>RAIZ4</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Azul</t>
+          <t>Raízen</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>11864400</v>
+        <v>15533300</v>
       </c>
       <c r="D28" t="n">
-        <v>1328874752</v>
+        <v>18394875904</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>USIM5</t>
+          <t>RADL3</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Usiminas</t>
+          <t>RaiaDrogasil</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>11715800</v>
+        <v>14644700</v>
       </c>
       <c r="D29" t="n">
-        <v>7267147776</v>
+        <v>32855148544</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>CRFB3</t>
+          <t>RENT3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Carrefour Brasil</t>
+          <t>Localiza</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>11618900</v>
+        <v>14413000</v>
       </c>
       <c r="D30" t="n">
-        <v>15691406336</v>
+        <v>34615685120</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>RAIL3</t>
+          <t>POMO4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rumo</t>
+          <t>Marcopolo</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>11497400</v>
+        <v>13669900</v>
       </c>
       <c r="D31" t="n">
-        <v>32091312128</v>
+        <v>7423169024</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>ANIM3</t>
+          <t>ELET3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ânima Educação</t>
+          <t>Eletrobras</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>10993900</v>
+        <v>13541000</v>
       </c>
       <c r="D32" t="n">
-        <v>694973568</v>
+        <v>91713478656</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>CSNA3</t>
+          <t>BHIA3</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Siderúrgica Nacional</t>
+          <t>Casas Bahia</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>10943300</v>
+        <v>12175600</v>
       </c>
       <c r="D33" t="n">
-        <v>11483938816</v>
+        <v>523835200</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>GGBR4</t>
+          <t>RAIL3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Gerdau</t>
+          <t>Rumo</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>9969500</v>
+        <v>12174600</v>
       </c>
       <c r="D34" t="n">
-        <v>33483960320</v>
+        <v>33313318912</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>NTCO3</t>
+          <t>AZZA3</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Natura</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>9539900</v>
+        <v>11682200</v>
       </c>
       <c r="D35" t="n">
-        <v>18102335488</v>
+        <v>4439083520</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>PETR3</t>
+          <t>CMIN3</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Petrobras</t>
+          <t>CSN Mineração</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>9512700</v>
+        <v>11473700</v>
       </c>
       <c r="D36" t="n">
-        <v>466225102848</v>
+        <v>33407045632</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>AZEV4</t>
+          <t>EZTC3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Azevedo &amp; Travassos</t>
+          <t>EZTEC</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>9354100</v>
+        <v>10777800</v>
       </c>
       <c r="D37" t="n">
-        <v>615288576</v>
+        <v>3411490816</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>CCRO3</t>
+          <t>MRVE3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Grupo CCR</t>
+          <t>MRV</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>8762100</v>
+        <v>10477600</v>
       </c>
       <c r="D38" t="n">
-        <v>23337492480</v>
+        <v>2825381632</v>
       </c>
     </row>
     <row r="39">
@@ -1128,1396 +1128,1396 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>8657600</v>
+        <v>10419100</v>
       </c>
       <c r="D39" t="n">
-        <v>18396676096</v>
+        <v>19545073664</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>PRIO3</t>
+          <t>BPAC11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PetroRio</t>
+          <t>Banco BTG Pactual</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8474100</v>
+        <v>10124600</v>
       </c>
       <c r="D40" t="n">
-        <v>31586787328</v>
+        <v>114362867712</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>BRFS3</t>
+          <t>BBDC3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BRF</t>
+          <t>Banco Bradesco</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>8322300</v>
+        <v>9505300</v>
       </c>
       <c r="D41" t="n">
-        <v>30477983744</v>
+        <v>122790699008</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>EQTL3</t>
+          <t>AZUL4</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Equatorial Energia</t>
+          <t>Azul</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>8225400</v>
+        <v>9331000</v>
       </c>
       <c r="D42" t="n">
-        <v>39043366912</v>
+        <v>1311481216</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>CYRE3</t>
+          <t>AURE3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cyrela</t>
+          <t>Auren Energia</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7958000</v>
+        <v>9254700</v>
       </c>
       <c r="D43" t="n">
-        <v>7926969856</v>
+        <v>7931398144</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>MRFG3</t>
+          <t>STBP3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Marfrig</t>
+          <t>Santos Brasil</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7942800</v>
+        <v>9133000</v>
       </c>
       <c r="D44" t="n">
-        <v>12903236608</v>
+        <v>11481511936</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>ELET3</t>
+          <t>PCAR3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Eletrobras</t>
+          <t>Grupo Pão de Açúcar</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>7677400</v>
+        <v>9053600</v>
       </c>
       <c r="D45" t="n">
-        <v>89286230016</v>
+        <v>1176271232</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>CMIG4</t>
+          <t>UGPA3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cemig</t>
+          <t>Ultrapar</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>7632900</v>
+        <v>9016300</v>
       </c>
       <c r="D46" t="n">
-        <v>35807973376</v>
+        <v>18525038592</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>WEGE3</t>
+          <t>ANIM3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>WEG</t>
+          <t>Ânima Educação</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7584000</v>
+        <v>8748200</v>
       </c>
       <c r="D47" t="n">
-        <v>200043347968</v>
+        <v>789399232</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>BEEF3</t>
+          <t>WEGE3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>WEG</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>7565600</v>
+        <v>8528600</v>
       </c>
       <c r="D48" t="n">
-        <v>2818081536</v>
+        <v>196101406720</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>HBSA3</t>
+          <t>BRFS3</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hidrovias do Brasil</t>
+          <t>BRF</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7345300</v>
+        <v>8492900</v>
       </c>
       <c r="D49" t="n">
-        <v>1612011776</v>
+        <v>28972380160</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>TIMS3</t>
+          <t>PETR3</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TIM</t>
+          <t>Petrobras</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7334400</v>
+        <v>8458900</v>
       </c>
       <c r="D50" t="n">
-        <v>41125994496</v>
+        <v>479206998016</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>EMBR3</t>
+          <t>RCSL4</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Embraer</t>
+          <t>Recrusul</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7316600</v>
+        <v>8317400</v>
       </c>
       <c r="D51" t="n">
-        <v>54546501632</v>
+        <v>56354284</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>BPAC11</t>
+          <t>BEEF3</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Banco BTG Pactual</t>
+          <t>Minerva</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7196000</v>
+        <v>7898800</v>
       </c>
       <c r="D52" t="n">
-        <v>107421573120</v>
+        <v>3159310592</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>FLRY3</t>
+          <t>EQTL3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fleury</t>
+          <t>Equatorial Energia</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7112600</v>
+        <v>7368700</v>
       </c>
       <c r="D53" t="n">
-        <v>5992522752</v>
+        <v>40203792384</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>CMIN3</t>
+          <t>GOAU4</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CSN Mineração</t>
+          <t>Metalúrgica Gerdau</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>6848200</v>
+        <v>7283100</v>
       </c>
       <c r="D54" t="n">
-        <v>29550297088</v>
+        <v>9424958464</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>UGPA3</t>
+          <t>ENEV3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ultrapar</t>
+          <t>Eneva</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>6803200</v>
+        <v>7206400</v>
       </c>
       <c r="D55" t="n">
-        <v>17096706048</v>
+        <v>24056467456</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>CEAB3</t>
+          <t>PETZ3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>C&amp;A</t>
+          <t>Petz</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6657400</v>
+        <v>6877700</v>
       </c>
       <c r="D56" t="n">
-        <v>3140473344</v>
+        <v>2093289600</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>PCAR3</t>
+          <t>SLCE3</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Grupo Pão de Açúcar</t>
+          <t>SLC Agrícola</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6405700</v>
+        <v>6845100</v>
       </c>
       <c r="D57" t="n">
-        <v>1205677952</v>
+        <v>8206150656</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>SIMH3</t>
+          <t>TOTS3</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Simpar</t>
+          <t>Totvs</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6065200</v>
+        <v>6714600</v>
       </c>
       <c r="D58" t="n">
-        <v>2821339392</v>
+        <v>19610107904</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>JBSS3</t>
+          <t>GGBR4</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JBS</t>
+          <t>Gerdau</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6048600</v>
+        <v>6674200</v>
       </c>
       <c r="D59" t="n">
-        <v>71734001664</v>
+        <v>33505134592</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>BBDC3</t>
+          <t>MULT3</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Banco Bradesco</t>
+          <t>Multiplan</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6027700</v>
+        <v>6566600</v>
       </c>
       <c r="D60" t="n">
-        <v>117455077376</v>
+        <v>11220012032</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>ENEV3</t>
+          <t>SUZB3</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Eneva</t>
+          <t>Suzano</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5995200</v>
+        <v>6516300</v>
       </c>
       <c r="D61" t="n">
-        <v>23081377792</v>
+        <v>67092451328</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>TOTS3</t>
+          <t>BRAV3</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Totvs</t>
+          <t>3R Petroleum</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>5957100</v>
+        <v>6325800</v>
       </c>
       <c r="D62" t="n">
-        <v>20061251584</v>
+        <v>8220644864</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>SUZB3</t>
+          <t>CRFB3</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Suzano</t>
+          <t>Carrefour Brasil</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>5896900</v>
+        <v>6265800</v>
       </c>
       <c r="D63" t="n">
-        <v>68889346048</v>
+        <v>15712496640</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>AURE3</t>
+          <t>INTB3</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Auren Energia</t>
+          <t>Intelbras</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>5692100</v>
+        <v>5908300</v>
       </c>
       <c r="D64" t="n">
-        <v>8109044736</v>
+        <v>3976189952</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>GOAU4</t>
+          <t>TEND3</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Metalúrgica Gerdau</t>
+          <t>Construtora Tenda</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>5691200</v>
+        <v>5897700</v>
       </c>
       <c r="D65" t="n">
-        <v>9252807680</v>
+        <v>1665835008</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>AMER3</t>
+          <t>MOVI3</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Americanas</t>
+          <t>Movida</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>5639800</v>
+        <v>5821400</v>
       </c>
       <c r="D66" t="n">
-        <v>1243515264</v>
+        <v>1449885568</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>MOVI3</t>
+          <t>SIMH3</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Movida</t>
+          <t>Simpar</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>5612400</v>
+        <v>5803700</v>
       </c>
       <c r="D67" t="n">
-        <v>1346670464</v>
+        <v>3118465280</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>MULT3</t>
+          <t>CPLE3</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Multiplan</t>
+          <t>Copel</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5448900</v>
+        <v>5736600</v>
       </c>
       <c r="D68" t="n">
-        <v>10491916288</v>
+        <v>29502402560</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>RDOR3</t>
+          <t>EMBR3</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Rede D'Or</t>
+          <t>Embraer</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>5447900</v>
+        <v>5653000</v>
       </c>
       <c r="D69" t="n">
-        <v>61177233408</v>
+        <v>55009316864</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>JHSF3</t>
+          <t>VIVA3</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JHSF</t>
+          <t>Vivara</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>5305600</v>
+        <v>5411200</v>
       </c>
       <c r="D70" t="n">
-        <v>2514694144</v>
+        <v>4195910144</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>BBSE3</t>
+          <t>CYRE3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BB Seguridade</t>
+          <t>Cyrela</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>5292500</v>
+        <v>5257900</v>
       </c>
       <c r="D71" t="n">
-        <v>75589935104</v>
+        <v>8432479744</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>PETZ3</t>
+          <t>AMER3</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Petz</t>
+          <t>Americanas</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>5142000</v>
+        <v>4929000</v>
       </c>
       <c r="D72" t="n">
-        <v>1962459008</v>
+        <v>1255529856</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>CPLE3</t>
+          <t>ALOS3</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Copel</t>
+          <t>Allos</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>5080500</v>
+        <v>4896100</v>
       </c>
       <c r="D73" t="n">
-        <v>28143132672</v>
+        <v>9584971776</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>ONCO3</t>
+          <t>QUAL3</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Oncoclínicas</t>
+          <t>Qualicorp</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>5017200</v>
+        <v>4838200</v>
       </c>
       <c r="D74" t="n">
-        <v>3366458880</v>
+        <v>489503776</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>GMAT3</t>
+          <t>ECOR3</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Grupo Mateus</t>
+          <t>EcoRodovias</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4774600</v>
+        <v>4657500</v>
       </c>
       <c r="D75" t="n">
-        <v>14035688448</v>
+        <v>3860696576</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>GFSA3</t>
+          <t>JBSS3</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Gafisa</t>
+          <t>JBS</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>4514800</v>
+        <v>4397200</v>
       </c>
       <c r="D76" t="n">
-        <v>106397192</v>
+        <v>73708126208</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>ALOS3</t>
+          <t>RDOR3</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Allos</t>
+          <t>Rede D'Or</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>4078700</v>
+        <v>4332000</v>
       </c>
       <c r="D77" t="n">
-        <v>9251017728</v>
+        <v>62643863552</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>STBP3</t>
+          <t>MRFG3</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Santos Brasil</t>
+          <t>Marfrig</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>4073600</v>
+        <v>4256200</v>
       </c>
       <c r="D78" t="n">
-        <v>11312274432</v>
+        <v>13085999104</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>VIVA3</t>
+          <t>SANB11</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Vivara</t>
+          <t>Banco Santander</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3903100</v>
+        <v>4210500</v>
       </c>
       <c r="D79" t="n">
-        <v>4165316352</v>
+        <v>137883582464</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>SLCE3</t>
+          <t>BBSE3</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SLC Agrícola</t>
+          <t>BB Seguridade</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3872500</v>
+        <v>4159500</v>
       </c>
       <c r="D80" t="n">
-        <v>8386844672</v>
+        <v>77279576064</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>LJQQ3</t>
+          <t>SBSP3</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Lojas Quero-Quero</t>
+          <t>Sabesp</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3808800</v>
+        <v>3892100</v>
       </c>
       <c r="D81" t="n">
-        <v>433758944</v>
+        <v>67872546816</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>CXSE3</t>
+          <t>SRNA3</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Caixa Seguridade</t>
+          <t>Serena Energia</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3805000</v>
+        <v>3826700</v>
       </c>
       <c r="D82" t="n">
-        <v>46020001792</v>
+        <v>4800924672</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>SANB11</t>
+          <t>CEAB3</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Banco Santander</t>
+          <t>C&amp;A</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3706100</v>
+        <v>3811700</v>
       </c>
       <c r="D83" t="n">
-        <v>135916822528</v>
+        <v>3241931008</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>CASH3</t>
+          <t>AZEV3</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Méliuz</t>
+          <t>Azevedo &amp; Travassos</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3655600</v>
+        <v>3777200</v>
       </c>
       <c r="D84" t="n">
-        <v>298990688</v>
+        <v>578351360</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>ECOR3</t>
+          <t>BRAP4</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EcoRodovias</t>
+          <t>Bradespar</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3551800</v>
+        <v>3754000</v>
       </c>
       <c r="D85" t="n">
-        <v>3735484672</v>
+        <v>6669442560</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>EZTC3</t>
+          <t>CBAV3</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EZTEC</t>
+          <t>CBA</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3476900</v>
+        <v>3744600</v>
       </c>
       <c r="D86" t="n">
-        <v>2887988224</v>
+        <v>3248854272</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>GOLL4</t>
+          <t>JHSF3</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GOL</t>
+          <t>JHSF</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3425100</v>
+        <v>3659400</v>
       </c>
       <c r="D87" t="n">
-        <v>4387109888</v>
+        <v>2629613056</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>KLBN11</t>
+          <t>LJQQ3</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Klabin</t>
+          <t>Lojas Quero-Quero</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3410700</v>
+        <v>3640300</v>
       </c>
       <c r="D88" t="n">
-        <v>128038387712</v>
+        <v>482116576</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>BRAP4</t>
+          <t>BRKM5</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Bradespar</t>
+          <t>Braskem</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3340100</v>
+        <v>3531100</v>
       </c>
       <c r="D89" t="n">
-        <v>6404996096</v>
+        <v>8874245120</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>VIVT3</t>
+          <t>YDUQ3</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Vivo</t>
+          <t>YDUQS</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3332600</v>
+        <v>3397800</v>
       </c>
       <c r="D90" t="n">
-        <v>82045100032</v>
+        <v>2968377600</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>SBSP3</t>
+          <t>TIMS3</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sabesp</t>
+          <t>TIM</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3290900</v>
+        <v>3385300</v>
       </c>
       <c r="D91" t="n">
-        <v>66191106048</v>
+        <v>41895391232</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>DXCO3</t>
+          <t>CXSE3</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Dexco</t>
+          <t>Caixa Seguridade</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3104200</v>
+        <v>3329200</v>
       </c>
       <c r="D92" t="n">
-        <v>4680433152</v>
+        <v>47550001152</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>TEND3</t>
+          <t>PGMN3</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Construtora Tenda</t>
+          <t>Pague Menos</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3101400</v>
+        <v>3284100</v>
       </c>
       <c r="D93" t="n">
-        <v>1785961472</v>
+        <v>1775971840</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>ALPA4</t>
+          <t>EVEN3</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Alpargatas</t>
+          <t>Even</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3048900</v>
+        <v>3149800</v>
       </c>
       <c r="D94" t="n">
-        <v>4488264704</v>
+        <v>1368149120</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>HYPE3</t>
+          <t>KLBN11</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Hypera</t>
+          <t>Klabin</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2999400</v>
+        <v>3103700</v>
       </c>
       <c r="D95" t="n">
-        <v>12016304128</v>
+        <v>128619708416</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>CLSA3</t>
+          <t>ONCO3</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ClearSale</t>
+          <t>Oncoclínicas</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2962800</v>
+        <v>3056100</v>
       </c>
       <c r="D96" t="n">
-        <v>1954217088</v>
+        <v>3442394112</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>SRNA3</t>
+          <t>SMFT3</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Serena Energia</t>
+          <t>Smart Fit</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2918300</v>
+        <v>3017900</v>
       </c>
       <c r="D97" t="n">
-        <v>5043772928</v>
+        <v>11765825536</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>CBAV3</t>
+          <t>CSMG3</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CBA</t>
+          <t>COPASA</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2903700</v>
+        <v>2921400</v>
       </c>
       <c r="D98" t="n">
-        <v>3398600960</v>
+        <v>9100343296</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>RAPT4</t>
+          <t>CPFE3</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Randon</t>
+          <t>CPFL Energia</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2886300</v>
+        <v>2901800</v>
       </c>
       <c r="D99" t="n">
-        <v>2926446336</v>
+        <v>43140239360</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>CPFE3</t>
+          <t>HYPE3</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CPFL Energia</t>
+          <t>Hypera</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2816700</v>
+        <v>2825500</v>
       </c>
       <c r="D100" t="n">
-        <v>43785498624</v>
+        <v>12846113792</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>BRKM5</t>
+          <t>VIVT3</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Braskem</t>
+          <t>Vivo</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2752500</v>
+        <v>2810300</v>
       </c>
       <c r="D101" t="n">
-        <v>8488827392</v>
+        <v>82932408320</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>OIBR3</t>
+          <t>CLSA3</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Oi</t>
+          <t>ClearSale</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2671800</v>
+        <v>2725300</v>
       </c>
       <c r="D102" t="n">
-        <v>393167712</v>
+        <v>1954217088</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>YDUQ3</t>
+          <t>GGPS3</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>YDUQS</t>
+          <t>GPS</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2664800</v>
+        <v>2660800</v>
       </c>
       <c r="D103" t="n">
-        <v>2882505216</v>
+        <v>9711163392</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>ENGI11</t>
+          <t>FLRY3</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Energisa</t>
+          <t>Fleury</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>2614000</v>
+        <v>2656800</v>
       </c>
       <c r="D104" t="n">
-        <v>17860067328</v>
+        <v>6294923264</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>QUAL3</t>
+          <t>ENGI11</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Qualicorp</t>
+          <t>Energisa</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2594600</v>
+        <v>2635600</v>
       </c>
       <c r="D105" t="n">
-        <v>512009696</v>
+        <v>18710331392</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>KEPL3</t>
+          <t>GMAT3</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Kepler Weber</t>
+          <t>Grupo Mateus</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2585400</v>
+        <v>2595300</v>
       </c>
       <c r="D106" t="n">
-        <v>1313371392</v>
+        <v>14484829184</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>PSSA3</t>
+          <t>ALPA4</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Porto Seguro</t>
+          <t>Alpargatas</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2565400</v>
+        <v>2439300</v>
       </c>
       <c r="D107" t="n">
-        <v>23950063616</v>
+        <v>4706683392</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>SMTO3</t>
+          <t>VVEO3</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>São Martinho</t>
+          <t>Viveo</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2403700</v>
+        <v>2407700</v>
       </c>
       <c r="D108" t="n">
-        <v>6920874496</v>
+        <v>464237760</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>RECV3</t>
+          <t>ELET6</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PetroRecôncavo</t>
+          <t>Eletrobras</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>2373700</v>
+        <v>2369500</v>
       </c>
       <c r="D109" t="n">
-        <v>4613692928</v>
+        <v>91713454080</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>INTB3</t>
+          <t>GOLL4</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Intelbras</t>
+          <t>GOL</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2351100</v>
+        <v>2052800</v>
       </c>
       <c r="D110" t="n">
-        <v>4081148416</v>
+        <v>4515200512</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>AZEV3</t>
+          <t>ENJU3</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Azevedo &amp; Travassos</t>
+          <t>Enjoei</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2346100</v>
+        <v>2007400</v>
       </c>
       <c r="D111" t="n">
-        <v>624024704</v>
+        <v>270623776</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>CAML3</t>
+          <t>DXCO3</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Camil Alimentos</t>
+          <t>Dexco</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2281200</v>
+        <v>1961200</v>
       </c>
       <c r="D112" t="n">
-        <v>1289248384</v>
+        <v>4518760448</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>MYPK3</t>
+          <t>HBSA3</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Iochpe-Maxion</t>
+          <t>Hidrovias do Brasil</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2266500</v>
+        <v>1944900</v>
       </c>
       <c r="D113" t="n">
-        <v>1970973184</v>
+        <v>1805490560</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>GGPS3</t>
+          <t>KEPL3</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>GPS</t>
+          <t>Kepler Weber</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>2254300</v>
+        <v>1940400</v>
       </c>
       <c r="D114" t="n">
-        <v>9198273536</v>
+        <v>1353223040</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>SMFT3</t>
+          <t>PTBL3</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Smart Fit</t>
+          <t>Portobello</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>2221500</v>
+        <v>1929800</v>
       </c>
       <c r="D115" t="n">
-        <v>11048252416</v>
+        <v>493454528</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>BRSR6</t>
+          <t>GFSA3</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Banrisul</t>
+          <t>Gafisa</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>2121100</v>
+        <v>1915700</v>
       </c>
       <c r="D116" t="n">
-        <v>4619170816</v>
+        <v>106397192</v>
       </c>
     </row>
     <row r="117">
@@ -2532,82 +2532,82 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>2092300</v>
+        <v>1884500</v>
       </c>
       <c r="D117" t="n">
-        <v>2547925248</v>
+        <v>2601059328</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>PGMN3</t>
+          <t>RAPT4</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Pague Menos</t>
+          <t>Randon</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>2084900</v>
+        <v>1877300</v>
       </c>
       <c r="D118" t="n">
-        <v>1798703616</v>
+        <v>2984699648</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>ISAE4</t>
+          <t>MYPK3</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ISA Energia</t>
+          <t>Iochpe-Maxion</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2043400</v>
+        <v>1875800</v>
       </c>
       <c r="D119" t="n">
-        <v>17846992896</v>
+        <v>2041365120</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>VVEO3</t>
+          <t>OIBR3</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Viveo</t>
+          <t>Oi</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1971800</v>
+        <v>1838700</v>
       </c>
       <c r="D120" t="n">
-        <v>435815040</v>
+        <v>396229568</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>KLBN4</t>
+          <t>ISAE4</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Klabin</t>
+          <t>ISA Energia</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1961300</v>
+        <v>1834700</v>
       </c>
       <c r="D121" t="n">
-        <v>24142223360</v>
+        <v>17129297920</v>
       </c>
     </row>
     <row r="122">
@@ -2622,2332 +2622,2314 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1893500</v>
+        <v>1794800</v>
       </c>
       <c r="D122" t="n">
-        <v>11547607040</v>
+        <v>11737080832</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>ALUP11</t>
+          <t>MTRE3</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Alupar</t>
+          <t>Mitre Realty</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1888100</v>
+        <v>1651700</v>
       </c>
       <c r="D123" t="n">
-        <v>14604174336</v>
+        <v>352230752</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>GUAR3</t>
+          <t>RECV3</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Guararapes</t>
+          <t>PetroRecôncavo</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1822300</v>
+        <v>1612600</v>
       </c>
       <c r="D124" t="n">
-        <v>3304684032</v>
+        <v>4792496128</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>RCSL3</t>
+          <t>KLBN4</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Recrusul</t>
+          <t>Klabin</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1805000</v>
+        <v>1564800</v>
       </c>
       <c r="D125" t="n">
-        <v>53644320</v>
+        <v>23981568000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>DIRR3</t>
+          <t>BRSR6</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Direcional</t>
+          <t>Banrisul</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1797900</v>
+        <v>1529300</v>
       </c>
       <c r="D126" t="n">
-        <v>5226801664</v>
+        <v>4810818560</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>CSMG3</t>
+          <t>DIRR3</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>COPASA</t>
+          <t>Direcional</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1774000</v>
+        <v>1453200</v>
       </c>
       <c r="D127" t="n">
-        <v>8626367488</v>
+        <v>5204250112</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>AZZA3</t>
+          <t>PORT3</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Wilson Sons</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1734900</v>
+        <v>1440200</v>
       </c>
       <c r="D128" t="n">
-        <v>5426005504</v>
+        <v>7650968064</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>EGIE3</t>
+          <t>PSSA3</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Engie</t>
+          <t>Porto Seguro</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1660500</v>
+        <v>1422200</v>
       </c>
       <c r="D129" t="n">
-        <v>30842077184</v>
+        <v>24942645248</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>GRND3</t>
+          <t>JSLG3</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Grendene</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1618000</v>
+        <v>1327200</v>
       </c>
       <c r="D130" t="n">
-        <v>5236454400</v>
+        <v>1547239424</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>SAPR4</t>
+          <t>IRBR3</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Sanepar</t>
+          <t>IRB Brasil RE</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1412500</v>
+        <v>1295500</v>
       </c>
       <c r="D131" t="n">
-        <v>8338074112</v>
+        <v>3972654336</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>ELET6</t>
+          <t>SAPR4</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Eletrobras</t>
+          <t>Sanepar</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1382500</v>
+        <v>1295100</v>
       </c>
       <c r="D132" t="n">
-        <v>89291218944</v>
+        <v>8442616320</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>CURY3</t>
+          <t>PLPL3</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Cury</t>
+          <t>Plano&amp;Plano</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1314400</v>
+        <v>1272200</v>
       </c>
       <c r="D133" t="n">
-        <v>6380346880</v>
+        <v>2183929600</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>EVEN3</t>
+          <t>CAML3</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Even</t>
+          <t>Camil Alimentos</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1290200</v>
+        <v>1243600</v>
       </c>
       <c r="D134" t="n">
-        <v>1234287104</v>
+        <v>1296069760</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>IRBR3</t>
+          <t>MLAS3</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>IRB Brasil RE</t>
+          <t>Multilaser</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1288000</v>
+        <v>1193700</v>
       </c>
       <c r="D135" t="n">
-        <v>3732035840</v>
+        <v>976969728</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>ODPV3</t>
+          <t>MEAL3</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Odontoprev</t>
+          <t>IMC Alimentação</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1271900</v>
+        <v>1183600</v>
       </c>
       <c r="D136" t="n">
-        <v>5785745408</v>
+        <v>313987328</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>AERI3</t>
+          <t>ALUP11</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Aeris Energy</t>
+          <t>Alupar</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1224800</v>
+        <v>1171200</v>
       </c>
       <c r="D137" t="n">
-        <v>223876400</v>
+        <v>14478958592</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>PLPL3</t>
+          <t>VLID3</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Plano&amp;Plano</t>
+          <t>Valid</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1145700</v>
+        <v>1165700</v>
       </c>
       <c r="D138" t="n">
-        <v>2137131136</v>
+        <v>1852208768</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>SAPR11</t>
+          <t>CURY3</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Sanepar</t>
+          <t>Cury</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1040400</v>
+        <v>1164300</v>
       </c>
       <c r="D139" t="n">
-        <v>8341851648</v>
+        <v>6762993664</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>POMO3</t>
+          <t>BPAN4</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Marcopolo</t>
+          <t>Banco Pan</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>982000</v>
+        <v>1142100</v>
       </c>
       <c r="D140" t="n">
-        <v>7243664896</v>
+        <v>9016609792</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>ARML3</t>
+          <t>GRND3</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Armac</t>
+          <t>Grendene</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>951500</v>
+        <v>1107600</v>
       </c>
       <c r="D141" t="n">
-        <v>1512671104</v>
+        <v>5245467136</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>RANI3</t>
+          <t>GUAR3</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Irani</t>
+          <t>Guararapes</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>936700</v>
+        <v>1089600</v>
       </c>
       <c r="D142" t="n">
-        <v>1783956992</v>
+        <v>3694057728</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>NEOE3</t>
+          <t>POSI3</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Neoenergia</t>
+          <t>Positivo</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>924900</v>
+        <v>1086400</v>
       </c>
       <c r="D143" t="n">
-        <v>24008435712</v>
+        <v>750354048</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>MLAS3</t>
+          <t>EGIE3</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Multilaser</t>
+          <t>Engie</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>910200</v>
+        <v>1063300</v>
       </c>
       <c r="D144" t="n">
-        <v>960821504</v>
+        <v>30817601536</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>BPAN4</t>
+          <t>DASA3</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Banco Pan</t>
+          <t>Dasa</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>908900</v>
+        <v>1034200</v>
       </c>
       <c r="D145" t="n">
-        <v>8628932608</v>
+        <v>2374334976</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>TTEN3</t>
+          <t>ZAMP3</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>3tentos</t>
+          <t>Zamp</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>897600</v>
+        <v>1032700</v>
       </c>
       <c r="D146" t="n">
-        <v>7157122048</v>
+        <v>1116953600</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>JALL3</t>
+          <t>TRIS3</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Jalles Machado</t>
+          <t>Trisul</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>885100</v>
+        <v>1020200</v>
       </c>
       <c r="D147" t="n">
-        <v>1218253952</v>
+        <v>1154943744</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>ITUB3</t>
+          <t>FESA4</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Itaú Unibanco</t>
+          <t>Ferbasa</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>847900</v>
+        <v>983500</v>
       </c>
       <c r="D148" t="n">
-        <v>302050050048</v>
+        <v>3052506624</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>AGXY3</t>
+          <t>ITUB3</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>AgroGalaxy</t>
+          <t>Itaú Unibanco</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>843100</v>
+        <v>969700</v>
       </c>
       <c r="D149" t="n">
-        <v>128085480</v>
+        <v>317262200832</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>MDIA3</t>
+          <t>TTEN3</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>M. Dias Branco</t>
+          <t>3tentos</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>814400</v>
+        <v>941700</v>
       </c>
       <c r="D150" t="n">
-        <v>8089027584</v>
+        <v>7042568704</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>MILS3</t>
+          <t>SAPR11</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Mills</t>
+          <t>Sanepar</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>776400</v>
+        <v>937800</v>
       </c>
       <c r="D151" t="n">
-        <v>2039116672</v>
+        <v>8399277568</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>ABCB4</t>
+          <t>ARML3</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Banco ABC Brasil</t>
+          <t>Armac</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>743100</v>
+        <v>933800</v>
       </c>
       <c r="D152" t="n">
-        <v>4728816640</v>
+        <v>1599208320</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>ZAMP3</t>
+          <t>SMTO3</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Zamp</t>
+          <t>São Martinho</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>677700</v>
+        <v>933600</v>
       </c>
       <c r="D153" t="n">
-        <v>1093018880</v>
+        <v>7294431744</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>DASA3</t>
+          <t>PRNR3</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Dasa</t>
+          <t>Priner</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>666400</v>
+        <v>903500</v>
       </c>
       <c r="D154" t="n">
-        <v>2161894656</v>
+        <v>815278016</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>MBLY3</t>
+          <t>DESK3</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Mobly</t>
+          <t>Desktop</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>666300</v>
+        <v>867900</v>
       </c>
       <c r="D155" t="n">
-        <v>159591888</v>
+        <v>970493952</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>SEQL3</t>
+          <t>TFCO4</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Sequoia Logística</t>
+          <t>Track &amp; Field</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>664400</v>
+        <v>864200</v>
       </c>
       <c r="D156" t="n">
-        <v>69921600</v>
+        <v>1507601920</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>PORT3</t>
+          <t>NEOE3</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Wilson Sons</t>
+          <t>Neoenergia</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>629500</v>
+        <v>851100</v>
       </c>
       <c r="D157" t="n">
-        <v>7412839424</v>
+        <v>25052829696</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>POSI3</t>
+          <t>VULC3</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Positivo</t>
+          <t>Vulcabras</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>581500</v>
+        <v>837500</v>
       </c>
       <c r="D158" t="n">
-        <v>733985664</v>
+        <v>4332592128</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>JSLG3</t>
+          <t>ODPV3</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>Odontoprev</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>579700</v>
+        <v>837200</v>
       </c>
       <c r="D159" t="n">
-        <v>1558616192</v>
+        <v>5965867520</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>SYNE3</t>
+          <t>ESPA3</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SYN</t>
+          <t>Espaçolaser</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>567200</v>
+        <v>790800</v>
       </c>
       <c r="D160" t="n">
-        <v>717426752</v>
+        <v>256610320</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>MTRE3</t>
+          <t>ABCB4</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Mitre Realty</t>
+          <t>Banco ABC Brasil</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>541600</v>
+        <v>761900</v>
       </c>
       <c r="D161" t="n">
-        <v>332133504</v>
+        <v>5012994048</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>TUPY3</t>
+          <t>SEQL3</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Tupy</t>
+          <t>Sequoia Logística</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>535400</v>
+        <v>750800</v>
       </c>
       <c r="D162" t="n">
-        <v>2889563392</v>
+        <v>72718464</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>LEVE3</t>
+          <t>UNIP6</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Mahle Metal Leve</t>
+          <t>Unipar</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>532000</v>
+        <v>712800</v>
       </c>
       <c r="D163" t="n">
-        <v>3968582144</v>
+        <v>5892864512</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>ESPA3</t>
+          <t>RCSL3</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Espaçolaser</t>
+          <t>Recrusul</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>530000</v>
+        <v>674600</v>
       </c>
       <c r="D164" t="n">
-        <v>249381872</v>
+        <v>56354256</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>VULC3</t>
+          <t>CASH3</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Vulcabras</t>
+          <t>Méliuz</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>490700</v>
+        <v>641800</v>
       </c>
       <c r="D165" t="n">
-        <v>4511311360</v>
+        <v>311194368</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>SEER3</t>
+          <t>OPCT3</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Ser Educacional</t>
+          <t>OceanPact</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>484400</v>
+        <v>633600</v>
       </c>
       <c r="D166" t="n">
-        <v>519077984</v>
+        <v>1070701248</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>LAVV3</t>
+          <t>MILS3</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Lavvi Incorporadora</t>
+          <t>Mills</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>483500</v>
+        <v>610400</v>
       </c>
       <c r="D167" t="n">
-        <v>1768677760</v>
+        <v>2140621312</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>MDNE3</t>
+          <t>LAVV3</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Moura Dubeux</t>
+          <t>Lavvi Incorporadora</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>461900</v>
+        <v>558000</v>
       </c>
       <c r="D168" t="n">
-        <v>1064428864</v>
+        <v>1850760064</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>DESK3</t>
+          <t>MDNE3</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Desktop</t>
+          <t>Moura Dubeux</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>444700</v>
+        <v>556400</v>
       </c>
       <c r="D169" t="n">
-        <v>984349760</v>
+        <v>1101306752</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>RNEW4</t>
+          <t>SHUL4</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Renova Energia</t>
+          <t>Schulz</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>440800</v>
+        <v>526900</v>
       </c>
       <c r="D170" t="n">
-        <v>220792864</v>
+        <v>1189951488</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>CSED3</t>
+          <t>HBRE3</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Cruzeiro do Sul Educacional</t>
+          <t>HBR Realty</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>420200</v>
+        <v>526400</v>
       </c>
       <c r="D171" t="n">
-        <v>1246737152</v>
+        <v>308703008</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>SOJA3</t>
+          <t>MELK3</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Boa Safra Sementes</t>
+          <t>Melnick</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>410400</v>
+        <v>508600</v>
       </c>
       <c r="D172" t="n">
-        <v>1388246400</v>
+        <v>815045312</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>FESA4</t>
+          <t>MBLY3</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ferbasa</t>
+          <t>Mobly</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>407400</v>
+        <v>507900</v>
       </c>
       <c r="D173" t="n">
-        <v>3014016768</v>
+        <v>147315600</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>ENJU3</t>
+          <t>SEER3</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Enjoei</t>
+          <t>Ser Educacional</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>404100</v>
+        <v>503800</v>
       </c>
       <c r="D174" t="n">
-        <v>239871056</v>
+        <v>559790016</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>TFCO4</t>
+          <t>JALL3</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Track &amp; Field</t>
+          <t>Jalles Machado</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>396600</v>
+        <v>494700</v>
       </c>
       <c r="D175" t="n">
-        <v>1522941440</v>
+        <v>1236346752</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>VLID3</t>
+          <t>MATD3</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Valid</t>
+          <t>Mater Dei</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>393600</v>
+        <v>487300</v>
       </c>
       <c r="D176" t="n">
-        <v>2072903424</v>
+        <v>1426952832</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>FIQE3</t>
+          <t>WIZC3</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Unifique</t>
+          <t>Wiz Soluções</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>374200</v>
+        <v>479800</v>
       </c>
       <c r="D177" t="n">
-        <v>1200369920</v>
+        <v>989824384</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>WIZC3</t>
+          <t>CSED3</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Wiz Soluções</t>
+          <t>Cruzeiro do Sul Educacional</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>361800</v>
+        <v>469900</v>
       </c>
       <c r="D178" t="n">
-        <v>969036480</v>
+        <v>1341518336</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>FRAS3</t>
+          <t>MDIA3</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Fras-le</t>
+          <t>M. Dias Branco</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>355300</v>
+        <v>447000</v>
       </c>
       <c r="D179" t="n">
-        <v>6832939520</v>
+        <v>7807437312</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>TRIS3</t>
+          <t>VTRU3</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Trisul</t>
+          <t>VITRUBREPCOM</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>348200</v>
+        <v>438500</v>
       </c>
       <c r="D180" t="n">
-        <v>1065134720</v>
+        <v>846048768</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>LOGG3</t>
+          <t>HBOR3</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>LOG CP</t>
+          <t>Helbor</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>330200</v>
+        <v>420600</v>
       </c>
       <c r="D181" t="n">
-        <v>1515841280</v>
+        <v>226906752</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>HBRE3</t>
+          <t>ORVR3</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>HBR Realty</t>
+          <t>Orizon</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>312900</v>
+        <v>415600</v>
       </c>
       <c r="D182" t="n">
-        <v>273716672</v>
+        <v>3620806656</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>ORVR3</t>
+          <t>AMAR3</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Orizon</t>
+          <t>Lojas Marisa</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>310500</v>
+        <v>405400</v>
       </c>
       <c r="D183" t="n">
-        <v>3511311616</v>
+        <v>816374400</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>VTRU3</t>
+          <t>SYNE3</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>VITRUBREPCOM</t>
+          <t>SYN</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>301300</v>
+        <v>404000</v>
       </c>
       <c r="D184" t="n">
-        <v>781893440</v>
+        <v>740323392</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>RNEW3</t>
+          <t>AERI3</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Renova Energia</t>
+          <t>Aeris Energy</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>299000</v>
+        <v>399400</v>
       </c>
       <c r="D185" t="n">
-        <v>218312160</v>
+        <v>241050480</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>AGRO3</t>
+          <t>TUPY3</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>BrasilAgro</t>
+          <t>Tupy</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>294100</v>
+        <v>382700</v>
       </c>
       <c r="D186" t="n">
-        <v>2119817984</v>
+        <v>2889404416</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>OPCT3</t>
+          <t>LIGT3</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>OceanPact</t>
+          <t>Light</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>283300</v>
+        <v>380200</v>
       </c>
       <c r="D187" t="n">
-        <v>1056704448</v>
+        <v>2052594688</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>MEAL3</t>
+          <t>BMGB4</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>IMC Alimentação</t>
+          <t>Banco BMG</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>280200</v>
+        <v>367100</v>
       </c>
       <c r="D188" t="n">
-        <v>271170848</v>
+        <v>2209949184</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>BMGB4</t>
+          <t>LOGG3</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Banco BMG</t>
+          <t>LOG CP</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>272200</v>
+        <v>359900</v>
       </c>
       <c r="D189" t="n">
-        <v>2205831424</v>
+        <v>1570337280</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>USIM3</t>
+          <t>CMIG3</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Usiminas</t>
+          <t>Cemig</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>267500</v>
+        <v>338200</v>
       </c>
       <c r="D190" t="n">
-        <v>7352725504</v>
+        <v>35083681792</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>VITT3</t>
+          <t>FRAS3</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Vittia</t>
+          <t>Fras-le</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>264600</v>
+        <v>333300</v>
       </c>
       <c r="D191" t="n">
-        <v>783683200</v>
+        <v>7043881984</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>MELK3</t>
+          <t>KLBN3</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Melnick</t>
+          <t>Klabin</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>262600</v>
+        <v>332300</v>
       </c>
       <c r="D192" t="n">
-        <v>776233600</v>
+        <v>23981590528</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>BMOB3</t>
+          <t>BLAU3</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Bemobi</t>
+          <t>Blau Farmacêutica</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>251900</v>
+        <v>318400</v>
       </c>
       <c r="D193" t="n">
-        <v>1214017408</v>
+        <v>2077090688</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>KLBN3</t>
+          <t>FIQE3</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Klabin</t>
+          <t>Unifique</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>246700</v>
+        <v>316400</v>
       </c>
       <c r="D194" t="n">
-        <v>24634902528</v>
+        <v>1228613888</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>PTBL3</t>
+          <t>RANI3</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Portobello</t>
+          <t>Irani</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>226300</v>
+        <v>312500</v>
       </c>
       <c r="D195" t="n">
-        <v>524471680</v>
+        <v>1702950912</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>PRNR3</t>
+          <t>SOJA3</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Priner</t>
+          <t>Boa Safra Sementes</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>225500</v>
+        <v>304300</v>
       </c>
       <c r="D196" t="n">
-        <v>761548992</v>
+        <v>1388246400</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>SHUL4</t>
+          <t>USIM3</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Schulz</t>
+          <t>Usiminas</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>224400</v>
+        <v>298500</v>
       </c>
       <c r="D197" t="n">
-        <v>1179728512</v>
+        <v>7217203200</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>PMAM3</t>
+          <t>LEVE3</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Paranapanema</t>
+          <t>Mahle Metal Leve</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>220300</v>
+        <v>285600</v>
       </c>
       <c r="D198" t="n">
-        <v>86603664</v>
+        <v>4087856384</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>LPSB3</t>
+          <t>VITT3</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Lopes</t>
+          <t>Vittia</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>218800</v>
+        <v>258000</v>
       </c>
       <c r="D199" t="n">
-        <v>170237120</v>
+        <v>790632832</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>CAMB3</t>
+          <t>PNVL3</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Cambuci</t>
+          <t>Dimed</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>217400</v>
+        <v>257400</v>
       </c>
       <c r="D200" t="n">
-        <v>438835296</v>
+        <v>1258770432</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>AMAR3</t>
+          <t>SANB4</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Lojas Marisa</t>
+          <t>Banco Santander</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>216300</v>
+        <v>244900</v>
       </c>
       <c r="D201" t="n">
-        <v>759895680</v>
+        <v>97784553472</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>TASA4</t>
+          <t>ELMD3</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Taurus</t>
+          <t>Eletromidia</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>204300</v>
+        <v>238600</v>
       </c>
       <c r="D202" t="n">
-        <v>1022089664</v>
+        <v>4165577984</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>ITSA3</t>
+          <t>SANB3</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Itaúsa</t>
+          <t>Banco Santander</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>200000</v>
+        <v>230600</v>
       </c>
       <c r="D203" t="n">
-        <v>98448089088</v>
+        <v>97784496128</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>PNVL3</t>
+          <t>POMO3</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Dimed</t>
+          <t>Marcopolo</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>196400</v>
+        <v>227300</v>
       </c>
       <c r="D204" t="n">
-        <v>1211063552</v>
+        <v>7423163904</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>SANB4</t>
+          <t>TASA4</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Banco Santander</t>
+          <t>Taurus</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>195600</v>
+        <v>221600</v>
       </c>
       <c r="D205" t="n">
-        <v>95500722176</v>
+        <v>1017344704</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>CMIG3</t>
+          <t>CAMB3</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Cemig</t>
+          <t>Cambuci</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>194700</v>
+        <v>217600</v>
       </c>
       <c r="D206" t="n">
-        <v>35764162560</v>
+        <v>431298080</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>HBOR3</t>
+          <t>BOBR4</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Helbor</t>
+          <t>Bombril</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>189000</v>
+        <v>204400</v>
       </c>
       <c r="D207" t="n">
-        <v>196387120</v>
+        <v>213835568</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>SANB3</t>
+          <t>BMOB3</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Banco Santander</t>
+          <t>Bemobi</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>176000</v>
+        <v>197700</v>
       </c>
       <c r="D208" t="n">
-        <v>95275933696</v>
+        <v>1263228032</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>TGMA3</t>
+          <t>TAEE4</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Tegma</t>
+          <t>Taesa</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>175000</v>
+        <v>187400</v>
       </c>
       <c r="D209" t="n">
-        <v>2207597568</v>
+        <v>11730226176</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>PINE4</t>
+          <t>ROMI3</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Banco Pine</t>
+          <t>Indústrias ROMI</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>166900</v>
+        <v>183900</v>
       </c>
       <c r="D210" t="n">
-        <v>1027307520</v>
+        <v>900960704</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>SAPR3</t>
+          <t>TGMA3</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Sanepar</t>
+          <t>Tegma</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>164000</v>
+        <v>175800</v>
       </c>
       <c r="D211" t="n">
-        <v>8465853952</v>
+        <v>2274194944</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>TAEE4</t>
+          <t>COCE5</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Taesa</t>
+          <t>Coelce</t>
         </is>
       </c>
       <c r="C212" t="n">
-        <v>162600</v>
+        <v>171400</v>
       </c>
       <c r="D212" t="n">
-        <v>11542567936</v>
+        <v>1882730880</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>PFRM3</t>
+          <t>TPIS3</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Profarma</t>
+          <t>Triunfo</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>157500</v>
+        <v>167200</v>
       </c>
       <c r="D213" t="n">
-        <v>828850368</v>
+        <v>189121984</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>MATD3</t>
+          <t>FICT3</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Mater Dei</t>
+          <t>Fictor Alimentos</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>147700</v>
+        <v>162800</v>
       </c>
       <c r="D214" t="n">
-        <v>1278972544</v>
+        <v>92296472</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>LIGT3</t>
+          <t>AMBP3</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Ambipar</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>146800</v>
+        <v>158100</v>
       </c>
       <c r="D215" t="n">
-        <v>2052594688</v>
+        <v>21726478336</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>BLAU3</t>
+          <t>AGRO3</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Blau Farmacêutica</t>
+          <t>BrasilAgro</t>
         </is>
       </c>
       <c r="C216" t="n">
-        <v>143600</v>
+        <v>155800</v>
       </c>
       <c r="D216" t="n">
-        <v>2229896448</v>
+        <v>2132767872</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>UNIP6</t>
+          <t>AGXY3</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Unipar</t>
+          <t>AgroGalaxy</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>139600</v>
+        <v>152600</v>
       </c>
       <c r="D217" t="n">
-        <v>5284201984</v>
+        <v>128085480</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>CSUD3</t>
+          <t>ITSA3</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>CSU Cardsystem</t>
+          <t>Itaúsa</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>125500</v>
+        <v>137500</v>
       </c>
       <c r="D218" t="n">
-        <v>662558400</v>
+        <v>102134398976</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>SCAR3</t>
+          <t>SAPR3</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>São Carlos</t>
+          <t>Sanepar</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>111200</v>
+        <v>122300</v>
       </c>
       <c r="D219" t="n">
-        <v>1008347776</v>
+        <v>8442608640</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>ETER3</t>
+          <t>PINE4</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Eternit</t>
+          <t>Banco Pine</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>110000</v>
+        <v>120500</v>
       </c>
       <c r="D220" t="n">
-        <v>322430016</v>
+        <v>1020324544</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>KRSA3</t>
+          <t>SCAR3</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Kora Saúde</t>
+          <t>São Carlos</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>104800</v>
+        <v>113700</v>
       </c>
       <c r="D221" t="n">
-        <v>672905664</v>
+        <v>1030081984</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>DMVF3</t>
+          <t>PFRM3</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>D1000 Varejo Farma</t>
+          <t>Profarma</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>94500</v>
+        <v>110200</v>
       </c>
       <c r="D222" t="n">
-        <v>297544480</v>
+        <v>899964736</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>ALLD3</t>
+          <t>LPSB3</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Allied</t>
+          <t>Lopes</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>94200</v>
+        <v>108800</v>
       </c>
       <c r="D223" t="n">
-        <v>633957632</v>
+        <v>182593040</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>LOGN3</t>
+          <t>PMAM3</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Log-In</t>
+          <t>Paranapanema</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>85000</v>
+        <v>107400</v>
       </c>
       <c r="D224" t="n">
-        <v>2239517696</v>
+        <v>86603664</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>UCAS3</t>
+          <t>RNEW4</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Unicasa</t>
+          <t>Renova Energia</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>84200</v>
+        <v>96900</v>
       </c>
       <c r="D225" t="n">
-        <v>91860096</v>
+        <v>215803504</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>DEXP3</t>
+          <t>TAEE3</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Dexxos</t>
+          <t>Taesa</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>82200</v>
+        <v>89800</v>
       </c>
       <c r="D226" t="n">
-        <v>868936000</v>
+        <v>11730226176</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>ALPK3</t>
+          <t>UCAS3</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Estapar</t>
+          <t>Unicasa</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>79300</v>
+        <v>88900</v>
       </c>
       <c r="D227" t="n">
-        <v>620936704</v>
+        <v>101773056</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>AMBP3</t>
+          <t>ETER3</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Ambipar</t>
+          <t>Eternit</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>79100</v>
+        <v>74200</v>
       </c>
       <c r="D228" t="n">
-        <v>22477676544</v>
+        <v>307633984</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>ELMD3</t>
+          <t>EALT4</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Eletromidia</t>
+          <t>Electro Aço Altona</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>76800</v>
+        <v>73900</v>
       </c>
       <c r="D229" t="n">
-        <v>4151646208</v>
+        <v>301080000</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>ROMI3</t>
+          <t>RNEW3</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Indústrias ROMI</t>
+          <t>Renova Energia</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>76500</v>
+        <v>72100</v>
       </c>
       <c r="D230" t="n">
-        <v>873941184</v>
+        <v>215803248</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>TECN3</t>
+          <t>LUPA3</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Technos</t>
+          <t>Lupatech</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>70700</v>
+        <v>71400</v>
       </c>
       <c r="D231" t="n">
-        <v>343607872</v>
+        <v>50989040</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>BRAP3</t>
+          <t>DEXP3</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Bradespar</t>
+          <t>Dexxos</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>64100</v>
+        <v>66300</v>
       </c>
       <c r="D232" t="n">
-        <v>6481973248</v>
+        <v>883818560</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>TAEE3</t>
+          <t>BRAP3</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Taesa</t>
+          <t>Bradespar</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>58800</v>
+        <v>62700</v>
       </c>
       <c r="D233" t="n">
-        <v>11470387200</v>
+        <v>6669444096</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>BIOM3</t>
+          <t>IGTI3</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Biomm</t>
+          <t>Jereissati Participações</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>50400</v>
+        <v>62100</v>
       </c>
       <c r="D234" t="n">
-        <v>1253189120</v>
+        <v>5093064192</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>VSTE3</t>
+          <t>IGTI3</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>LE LIS BLANC</t>
+          <t>Iguatemi</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>49700</v>
+        <v>62100</v>
       </c>
       <c r="D235" t="n">
-        <v>769506752</v>
+        <v>5093064192</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>TCSA3</t>
+          <t>TECN3</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Tecnisa</t>
+          <t>Technos</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>41100</v>
+        <v>52700</v>
       </c>
       <c r="D236" t="n">
-        <v>100858304</v>
+        <v>333557216</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>NGRD3</t>
+          <t>ALPK3</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Neogrid</t>
+          <t>Estapar</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>36500</v>
+        <v>49600</v>
       </c>
       <c r="D237" t="n">
-        <v>198911760</v>
+        <v>625248768</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>ENGI4</t>
+          <t>CSUD3</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Energisa</t>
+          <t>CSU Cardsystem</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>32400</v>
+        <v>47600</v>
       </c>
       <c r="D238" t="n">
-        <v>20101984256</v>
+        <v>677006720</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>EUCA4</t>
+          <t>DMVF3</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Eucatex</t>
+          <t>D1000 Varejo Farma</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>31900</v>
+        <v>47300</v>
       </c>
       <c r="D239" t="n">
-        <v>1259808512</v>
+        <v>303616800</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>BOBR4</t>
+          <t>LOGN3</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Bombril</t>
+          <t>Log-In</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>31800</v>
+        <v>41100</v>
       </c>
       <c r="D240" t="n">
-        <v>200317216</v>
+        <v>2280891904</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>AALR3</t>
+          <t>TCSA3</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Alliança</t>
+          <t>Tecnisa</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>31300</v>
+        <v>39100</v>
       </c>
       <c r="D241" t="n">
-        <v>1910975872</v>
+        <v>106011656</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>LVTC3</t>
+          <t>GOAU3</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>WDC Networks</t>
+          <t>Metalúrgica Gerdau</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>29600</v>
+        <v>38900</v>
       </c>
       <c r="D242" t="n">
-        <v>140249920</v>
+        <v>9424949248</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>BRKM3</t>
+          <t>RSID3</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Braskem</t>
+          <t>Rossi Residencial</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>29300</v>
+        <v>38700</v>
       </c>
       <c r="D243" t="n">
-        <v>8664183808</v>
+        <v>57684308</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>FHER3</t>
+          <t>BIOM3</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Fertilizantes Heringer</t>
+          <t>Biomm</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>28800</v>
+        <v>38600</v>
       </c>
       <c r="D244" t="n">
-        <v>227816384</v>
+        <v>1291241472</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>GOAU3</t>
+          <t>LVTC3</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Metalúrgica Gerdau</t>
+          <t>WDC Networks</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>28000</v>
+        <v>26100</v>
       </c>
       <c r="D245" t="n">
-        <v>9184176128</v>
+        <v>155480672</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>GGBR3</t>
+          <t>ALPA3</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Gerdau</t>
+          <t>Alpargatas</t>
         </is>
       </c>
       <c r="C246" t="n">
         <v>25500</v>
       </c>
       <c r="D246" t="n">
-        <v>33491113984</v>
+        <v>4706682368</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>IGTI3</t>
+          <t>INEP3</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Iguatemi</t>
+          <t>Inepar</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>24700</v>
+        <v>25400</v>
       </c>
       <c r="D247" t="n">
-        <v>4975718912</v>
+        <v>65073812</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>IGTI3</t>
+          <t>ENGI4</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Jereissati Participações</t>
+          <t>Energisa</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>24700</v>
+        <v>24400</v>
       </c>
       <c r="D248" t="n">
-        <v>4975718912</v>
+        <v>20799023104</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>RAPT3</t>
+          <t>ALLD3</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Randon</t>
+          <t>Allied</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>24100</v>
+        <v>23200</v>
       </c>
       <c r="D249" t="n">
-        <v>2969119232</v>
+        <v>663115968</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>SNSY5</t>
+          <t>KRSA3</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Sansuy</t>
+          <t>Kora Saúde</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>23100</v>
+        <v>20700</v>
       </c>
       <c r="D250" t="n">
-        <v>55452980</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="1" t="inlineStr">
-        <is>
-          <t>FICT3</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Fictor Alimentos</t>
-        </is>
-      </c>
-      <c r="C251" t="n">
-        <v>21600</v>
-      </c>
-      <c r="D251" t="n">
-        <v>95107528</v>
+        <v>674443776</v>
       </c>
     </row>
   </sheetData>

--- a/Bases/Lista de ações Tratada.xlsx
+++ b/Bases/Lista de ações Tratada.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D250"/>
+  <dimension ref="A1:D249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Volume no último dia útil (lido em 15/03/2025)</t>
+          <t>Volume no último dia útil (lido em 16/03/2025)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>42086800</v>
+        <v>42077200</v>
       </c>
       <c r="D7" t="n">
         <v>122790780928</v>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26742900</v>
+        <v>26742800</v>
       </c>
       <c r="D17" t="n">
         <v>13552640000</v>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22864500</v>
+        <v>22864700</v>
       </c>
       <c r="D20" t="n">
         <v>159137906688</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2439300</v>
+        <v>2439400</v>
       </c>
       <c r="D107" t="n">
         <v>4706683392</v>
@@ -4647,288 +4647,270 @@
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>IGTI3</t>
+          <t>TECN3</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Iguatemi</t>
+          <t>Technos</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>62100</v>
+        <v>52700</v>
       </c>
       <c r="D235" t="n">
-        <v>5093064192</v>
+        <v>333557216</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>TECN3</t>
+          <t>ALPK3</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Technos</t>
+          <t>Estapar</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>52700</v>
+        <v>49600</v>
       </c>
       <c r="D236" t="n">
-        <v>333557216</v>
+        <v>625248768</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>ALPK3</t>
+          <t>CSUD3</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Estapar</t>
+          <t>CSU Cardsystem</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>49600</v>
+        <v>47600</v>
       </c>
       <c r="D237" t="n">
-        <v>625248768</v>
+        <v>677006720</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>CSUD3</t>
+          <t>DMVF3</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>CSU Cardsystem</t>
+          <t>D1000 Varejo Farma</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>47600</v>
+        <v>47300</v>
       </c>
       <c r="D238" t="n">
-        <v>677006720</v>
+        <v>303616800</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>DMVF3</t>
+          <t>LOGN3</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>D1000 Varejo Farma</t>
+          <t>Log-In</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>47300</v>
+        <v>41100</v>
       </c>
       <c r="D239" t="n">
-        <v>303616800</v>
+        <v>2280891904</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>LOGN3</t>
+          <t>TCSA3</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Log-In</t>
+          <t>Tecnisa</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>41100</v>
+        <v>39100</v>
       </c>
       <c r="D240" t="n">
-        <v>2280891904</v>
+        <v>106011656</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>TCSA3</t>
+          <t>GOAU3</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Tecnisa</t>
+          <t>Metalúrgica Gerdau</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>39100</v>
+        <v>38900</v>
       </c>
       <c r="D241" t="n">
-        <v>106011656</v>
+        <v>9424949248</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>GOAU3</t>
+          <t>RSID3</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Metalúrgica Gerdau</t>
+          <t>Rossi Residencial</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>38900</v>
+        <v>38700</v>
       </c>
       <c r="D242" t="n">
-        <v>9424949248</v>
+        <v>57684308</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>RSID3</t>
+          <t>BIOM3</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Rossi Residencial</t>
+          <t>Biomm</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>38700</v>
+        <v>38600</v>
       </c>
       <c r="D243" t="n">
-        <v>57684308</v>
+        <v>1291241472</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>BIOM3</t>
+          <t>LVTC3</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Biomm</t>
+          <t>WDC Networks</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>38600</v>
+        <v>26100</v>
       </c>
       <c r="D244" t="n">
-        <v>1291241472</v>
+        <v>155480672</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>LVTC3</t>
+          <t>ALPA3</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>WDC Networks</t>
+          <t>Alpargatas</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>26100</v>
+        <v>25500</v>
       </c>
       <c r="D245" t="n">
-        <v>155480672</v>
+        <v>4706682368</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>ALPA3</t>
+          <t>INEP3</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Alpargatas</t>
+          <t>Inepar</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>25500</v>
+        <v>25400</v>
       </c>
       <c r="D246" t="n">
-        <v>4706682368</v>
+        <v>65073812</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>INEP3</t>
+          <t>ENGI4</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Inepar</t>
+          <t>Energisa</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>25400</v>
+        <v>24400</v>
       </c>
       <c r="D247" t="n">
-        <v>65073812</v>
+        <v>20799023104</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>ENGI4</t>
+          <t>ALLD3</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Energisa</t>
+          <t>Allied</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>24400</v>
+        <v>23200</v>
       </c>
       <c r="D248" t="n">
-        <v>20799023104</v>
+        <v>663115968</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>ALLD3</t>
+          <t>KRSA3</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Allied</t>
+          <t>Kora Saúde</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>23200</v>
+        <v>20700</v>
       </c>
       <c r="D249" t="n">
-        <v>663115968</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="1" t="inlineStr">
-        <is>
-          <t>KRSA3</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Kora Saúde</t>
-        </is>
-      </c>
-      <c r="C250" t="n">
-        <v>20700</v>
-      </c>
-      <c r="D250" t="n">
         <v>674443776</v>
       </c>
     </row>

--- a/Bases/Lista de ações Tratada.xlsx
+++ b/Bases/Lista de ações Tratada.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D249"/>
+  <dimension ref="A1:E249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,20 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Nome da Empresa</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Volume no último dia útil (lido em 16/03/2025)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Market Cap</t>
         </is>
@@ -456,15 +461,18 @@
           <t>B3SA3</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>B3</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>126021900</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>67275739136</v>
       </c>
     </row>
@@ -474,15 +482,18 @@
           <t>HAPV3</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Hapvida</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>111755000</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>16175141888</v>
       </c>
     </row>
@@ -492,15 +503,18 @@
           <t>NTCO3</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>Natura</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>105384100</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>13171654656</v>
       </c>
     </row>
@@ -510,15 +524,18 @@
           <t>COGN3</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>Cogna</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>102051600</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>3164490240</v>
       </c>
     </row>
@@ -528,15 +545,18 @@
           <t>MGLU3</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Magazine Luiza</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>65687600</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>7071379456</v>
       </c>
     </row>
@@ -546,15 +566,18 @@
           <t>BBDC4</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Banco Bradesco</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>42077200</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>122790780928</v>
       </c>
     </row>
@@ -564,15 +587,18 @@
           <t>ABEV3</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>Ambev</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>41765100</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>213556019200</v>
       </c>
     </row>
@@ -582,15 +608,18 @@
           <t>PETR4</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Petrobras</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>41510300</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>479207391232</v>
       </c>
     </row>
@@ -600,15 +629,18 @@
           <t>AMOB3</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Automob</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>35798400</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>530404000</v>
       </c>
     </row>
@@ -618,15 +650,18 @@
           <t>ITSA4</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Itaúsa</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>35728500</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>102134104064</v>
       </c>
     </row>
@@ -636,15 +671,18 @@
           <t>CCRO3</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Grupo CCR</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>32515300</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>23500873728</v>
       </c>
     </row>
@@ -654,15 +692,18 @@
           <t>VALE3</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Vale</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>31782000</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>240289628160</v>
       </c>
     </row>
@@ -672,15 +713,18 @@
           <t>ITUB4</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Itaú Unibanco</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>31638000</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>317260791808</v>
       </c>
     </row>
@@ -690,15 +734,18 @@
           <t>CMIG4</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Cemig</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>28449400</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>35083624448</v>
       </c>
     </row>
@@ -708,15 +755,18 @@
           <t>LWSA3</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Locaweb</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>27984300</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>1480759168</v>
       </c>
     </row>
@@ -726,15 +776,18 @@
           <t>CSNA3</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Siderúrgica Nacional</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>26742800</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>13552640000</v>
       </c>
     </row>
@@ -744,15 +797,18 @@
           <t>AZEV4</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Azevedo &amp; Travassos</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>23465200</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>578351232</v>
       </c>
     </row>
@@ -762,15 +818,18 @@
           <t>LREN3</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Lojas Renner</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>23036000</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>12406659072</v>
       </c>
     </row>
@@ -780,15 +839,18 @@
           <t>BBAS3</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Banco do Brasil</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>22864700</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>159137906688</v>
       </c>
     </row>
@@ -798,15 +860,18 @@
           <t>VAMO3</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>Grupo Vamos</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>20637800</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>4228711936</v>
       </c>
     </row>
@@ -816,15 +881,18 @@
           <t>CSAN3</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>Cosan</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>19310200</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>13884040192</v>
       </c>
     </row>
@@ -834,15 +902,18 @@
           <t>USIM5</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>Usiminas</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>18908100</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>7217229824</v>
       </c>
     </row>
@@ -852,15 +923,18 @@
           <t>ASAI3</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>Assaí</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>17930500</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>10180571136</v>
       </c>
     </row>
@@ -870,15 +944,18 @@
           <t>CVCB3</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>CVC</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>17711400</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>1060047488</v>
       </c>
     </row>
@@ -888,15 +965,18 @@
           <t>CPLE6</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" t="n">
+        <v>24</v>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Copel</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>16997000</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>29502375936</v>
       </c>
     </row>
@@ -906,15 +986,18 @@
           <t>PRIO3</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>PetroRio</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>16461300</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>33118572544</v>
       </c>
     </row>
@@ -924,15 +1007,18 @@
           <t>RAIZ4</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>Raízen</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>15533300</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>18394875904</v>
       </c>
     </row>
@@ -942,15 +1028,18 @@
           <t>RADL3</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" t="n">
+        <v>27</v>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>RaiaDrogasil</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>14644700</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>32855148544</v>
       </c>
     </row>
@@ -960,15 +1049,18 @@
           <t>RENT3</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" t="n">
+        <v>28</v>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>Localiza</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" t="n">
         <v>14413000</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>34615685120</v>
       </c>
     </row>
@@ -978,15 +1070,18 @@
           <t>POMO4</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" t="n">
+        <v>29</v>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>Marcopolo</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="D31" t="n">
         <v>13669900</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>7423169024</v>
       </c>
     </row>
@@ -996,15 +1091,18 @@
           <t>ELET3</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>Eletrobras</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="D32" t="n">
         <v>13541000</v>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>91713478656</v>
       </c>
     </row>
@@ -1014,15 +1112,18 @@
           <t>BHIA3</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>Casas Bahia</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="D33" t="n">
         <v>12175600</v>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
         <v>523835200</v>
       </c>
     </row>
@@ -1032,15 +1133,18 @@
           <t>RAIL3</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Rumo</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="D34" t="n">
         <v>12174600</v>
       </c>
-      <c r="D34" t="n">
+      <c r="E34" t="n">
         <v>33313318912</v>
       </c>
     </row>
@@ -1050,15 +1154,18 @@
           <t>AZZA3</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" t="n">
+        <v>33</v>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>Arezzo</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="D35" t="n">
         <v>11682200</v>
       </c>
-      <c r="D35" t="n">
+      <c r="E35" t="n">
         <v>4439083520</v>
       </c>
     </row>
@@ -1068,15 +1175,18 @@
           <t>CMIN3</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" t="n">
+        <v>34</v>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>CSN Mineração</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="D36" t="n">
         <v>11473700</v>
       </c>
-      <c r="D36" t="n">
+      <c r="E36" t="n">
         <v>33407045632</v>
       </c>
     </row>
@@ -1086,15 +1196,18 @@
           <t>EZTC3</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" t="n">
+        <v>35</v>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>EZTEC</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="D37" t="n">
         <v>10777800</v>
       </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
         <v>3411490816</v>
       </c>
     </row>
@@ -1104,15 +1217,18 @@
           <t>MRVE3</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" t="n">
+        <v>36</v>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>MRV</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="D38" t="n">
         <v>10477600</v>
       </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
         <v>2825381632</v>
       </c>
     </row>
@@ -1122,15 +1238,18 @@
           <t>VBBR3</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" t="n">
+        <v>37</v>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>Vibra Energia</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="D39" t="n">
         <v>10419100</v>
       </c>
-      <c r="D39" t="n">
+      <c r="E39" t="n">
         <v>19545073664</v>
       </c>
     </row>
@@ -1140,15 +1259,18 @@
           <t>BPAC11</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" t="n">
+        <v>38</v>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>Banco BTG Pactual</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="D40" t="n">
         <v>10124600</v>
       </c>
-      <c r="D40" t="n">
+      <c r="E40" t="n">
         <v>114362867712</v>
       </c>
     </row>
@@ -1158,15 +1280,18 @@
           <t>BBDC3</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" t="n">
+        <v>39</v>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>Banco Bradesco</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="D41" t="n">
         <v>9505300</v>
       </c>
-      <c r="D41" t="n">
+      <c r="E41" t="n">
         <v>122790699008</v>
       </c>
     </row>
@@ -1176,15 +1301,18 @@
           <t>AZUL4</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" t="n">
+        <v>40</v>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>Azul</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="D42" t="n">
         <v>9331000</v>
       </c>
-      <c r="D42" t="n">
+      <c r="E42" t="n">
         <v>1311481216</v>
       </c>
     </row>
@@ -1194,15 +1322,18 @@
           <t>AURE3</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" t="n">
+        <v>41</v>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>Auren Energia</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="D43" t="n">
         <v>9254700</v>
       </c>
-      <c r="D43" t="n">
+      <c r="E43" t="n">
         <v>7931398144</v>
       </c>
     </row>
@@ -1212,15 +1343,18 @@
           <t>STBP3</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" t="n">
+        <v>42</v>
+      </c>
+      <c r="C44" t="inlineStr">
         <is>
           <t>Santos Brasil</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="D44" t="n">
         <v>9133000</v>
       </c>
-      <c r="D44" t="n">
+      <c r="E44" t="n">
         <v>11481511936</v>
       </c>
     </row>
@@ -1230,15 +1364,18 @@
           <t>PCAR3</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" t="n">
+        <v>43</v>
+      </c>
+      <c r="C45" t="inlineStr">
         <is>
           <t>Grupo Pão de Açúcar</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="D45" t="n">
         <v>9053600</v>
       </c>
-      <c r="D45" t="n">
+      <c r="E45" t="n">
         <v>1176271232</v>
       </c>
     </row>
@@ -1248,15 +1385,18 @@
           <t>UGPA3</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" t="n">
+        <v>44</v>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>Ultrapar</t>
         </is>
       </c>
-      <c r="C46" t="n">
+      <c r="D46" t="n">
         <v>9016300</v>
       </c>
-      <c r="D46" t="n">
+      <c r="E46" t="n">
         <v>18525038592</v>
       </c>
     </row>
@@ -1266,15 +1406,18 @@
           <t>ANIM3</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" t="n">
+        <v>45</v>
+      </c>
+      <c r="C47" t="inlineStr">
         <is>
           <t>Ânima Educação</t>
         </is>
       </c>
-      <c r="C47" t="n">
+      <c r="D47" t="n">
         <v>8748200</v>
       </c>
-      <c r="D47" t="n">
+      <c r="E47" t="n">
         <v>789399232</v>
       </c>
     </row>
@@ -1284,15 +1427,18 @@
           <t>WEGE3</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" t="n">
+        <v>46</v>
+      </c>
+      <c r="C48" t="inlineStr">
         <is>
           <t>WEG</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="D48" t="n">
         <v>8528600</v>
       </c>
-      <c r="D48" t="n">
+      <c r="E48" t="n">
         <v>196101406720</v>
       </c>
     </row>
@@ -1302,15 +1448,18 @@
           <t>BRFS3</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" t="n">
+        <v>47</v>
+      </c>
+      <c r="C49" t="inlineStr">
         <is>
           <t>BRF</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="D49" t="n">
         <v>8492900</v>
       </c>
-      <c r="D49" t="n">
+      <c r="E49" t="n">
         <v>28972380160</v>
       </c>
     </row>
@@ -1320,15 +1469,18 @@
           <t>PETR3</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" t="n">
+        <v>48</v>
+      </c>
+      <c r="C50" t="inlineStr">
         <is>
           <t>Petrobras</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="D50" t="n">
         <v>8458900</v>
       </c>
-      <c r="D50" t="n">
+      <c r="E50" t="n">
         <v>479206998016</v>
       </c>
     </row>
@@ -1338,15 +1490,18 @@
           <t>RCSL4</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" t="n">
+        <v>49</v>
+      </c>
+      <c r="C51" t="inlineStr">
         <is>
           <t>Recrusul</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="D51" t="n">
         <v>8317400</v>
       </c>
-      <c r="D51" t="n">
+      <c r="E51" t="n">
         <v>56354284</v>
       </c>
     </row>
@@ -1356,15 +1511,18 @@
           <t>BEEF3</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" t="n">
+        <v>50</v>
+      </c>
+      <c r="C52" t="inlineStr">
         <is>
           <t>Minerva</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="D52" t="n">
         <v>7898800</v>
       </c>
-      <c r="D52" t="n">
+      <c r="E52" t="n">
         <v>3159310592</v>
       </c>
     </row>
@@ -1374,15 +1532,18 @@
           <t>EQTL3</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" t="n">
+        <v>51</v>
+      </c>
+      <c r="C53" t="inlineStr">
         <is>
           <t>Equatorial Energia</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="D53" t="n">
         <v>7368700</v>
       </c>
-      <c r="D53" t="n">
+      <c r="E53" t="n">
         <v>40203792384</v>
       </c>
     </row>
@@ -1392,15 +1553,18 @@
           <t>GOAU4</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" t="n">
+        <v>52</v>
+      </c>
+      <c r="C54" t="inlineStr">
         <is>
           <t>Metalúrgica Gerdau</t>
         </is>
       </c>
-      <c r="C54" t="n">
+      <c r="D54" t="n">
         <v>7283100</v>
       </c>
-      <c r="D54" t="n">
+      <c r="E54" t="n">
         <v>9424958464</v>
       </c>
     </row>
@@ -1410,15 +1574,18 @@
           <t>ENEV3</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" t="n">
+        <v>53</v>
+      </c>
+      <c r="C55" t="inlineStr">
         <is>
           <t>Eneva</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="D55" t="n">
         <v>7206400</v>
       </c>
-      <c r="D55" t="n">
+      <c r="E55" t="n">
         <v>24056467456</v>
       </c>
     </row>
@@ -1428,15 +1595,18 @@
           <t>PETZ3</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" t="n">
+        <v>54</v>
+      </c>
+      <c r="C56" t="inlineStr">
         <is>
           <t>Petz</t>
         </is>
       </c>
-      <c r="C56" t="n">
+      <c r="D56" t="n">
         <v>6877700</v>
       </c>
-      <c r="D56" t="n">
+      <c r="E56" t="n">
         <v>2093289600</v>
       </c>
     </row>
@@ -1446,15 +1616,18 @@
           <t>SLCE3</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" t="n">
+        <v>55</v>
+      </c>
+      <c r="C57" t="inlineStr">
         <is>
           <t>SLC Agrícola</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="D57" t="n">
         <v>6845100</v>
       </c>
-      <c r="D57" t="n">
+      <c r="E57" t="n">
         <v>8206150656</v>
       </c>
     </row>
@@ -1464,15 +1637,18 @@
           <t>TOTS3</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" t="n">
+        <v>56</v>
+      </c>
+      <c r="C58" t="inlineStr">
         <is>
           <t>Totvs</t>
         </is>
       </c>
-      <c r="C58" t="n">
+      <c r="D58" t="n">
         <v>6714600</v>
       </c>
-      <c r="D58" t="n">
+      <c r="E58" t="n">
         <v>19610107904</v>
       </c>
     </row>
@@ -1482,15 +1658,18 @@
           <t>GGBR4</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" t="n">
+        <v>57</v>
+      </c>
+      <c r="C59" t="inlineStr">
         <is>
           <t>Gerdau</t>
         </is>
       </c>
-      <c r="C59" t="n">
+      <c r="D59" t="n">
         <v>6674200</v>
       </c>
-      <c r="D59" t="n">
+      <c r="E59" t="n">
         <v>33505134592</v>
       </c>
     </row>
@@ -1500,15 +1679,18 @@
           <t>MULT3</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" t="n">
+        <v>58</v>
+      </c>
+      <c r="C60" t="inlineStr">
         <is>
           <t>Multiplan</t>
         </is>
       </c>
-      <c r="C60" t="n">
+      <c r="D60" t="n">
         <v>6566600</v>
       </c>
-      <c r="D60" t="n">
+      <c r="E60" t="n">
         <v>11220012032</v>
       </c>
     </row>
@@ -1518,15 +1700,18 @@
           <t>SUZB3</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" t="n">
+        <v>59</v>
+      </c>
+      <c r="C61" t="inlineStr">
         <is>
           <t>Suzano</t>
         </is>
       </c>
-      <c r="C61" t="n">
+      <c r="D61" t="n">
         <v>6516300</v>
       </c>
-      <c r="D61" t="n">
+      <c r="E61" t="n">
         <v>67092451328</v>
       </c>
     </row>
@@ -1536,15 +1721,18 @@
           <t>BRAV3</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" t="n">
+        <v>60</v>
+      </c>
+      <c r="C62" t="inlineStr">
         <is>
           <t>3R Petroleum</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="D62" t="n">
         <v>6325800</v>
       </c>
-      <c r="D62" t="n">
+      <c r="E62" t="n">
         <v>8220644864</v>
       </c>
     </row>
@@ -1554,15 +1742,18 @@
           <t>CRFB3</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" t="n">
+        <v>61</v>
+      </c>
+      <c r="C63" t="inlineStr">
         <is>
           <t>Carrefour Brasil</t>
         </is>
       </c>
-      <c r="C63" t="n">
+      <c r="D63" t="n">
         <v>6265800</v>
       </c>
-      <c r="D63" t="n">
+      <c r="E63" t="n">
         <v>15712496640</v>
       </c>
     </row>
@@ -1572,15 +1763,18 @@
           <t>INTB3</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" t="n">
+        <v>62</v>
+      </c>
+      <c r="C64" t="inlineStr">
         <is>
           <t>Intelbras</t>
         </is>
       </c>
-      <c r="C64" t="n">
+      <c r="D64" t="n">
         <v>5908300</v>
       </c>
-      <c r="D64" t="n">
+      <c r="E64" t="n">
         <v>3976189952</v>
       </c>
     </row>
@@ -1590,15 +1784,18 @@
           <t>TEND3</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" t="n">
+        <v>63</v>
+      </c>
+      <c r="C65" t="inlineStr">
         <is>
           <t>Construtora Tenda</t>
         </is>
       </c>
-      <c r="C65" t="n">
+      <c r="D65" t="n">
         <v>5897700</v>
       </c>
-      <c r="D65" t="n">
+      <c r="E65" t="n">
         <v>1665835008</v>
       </c>
     </row>
@@ -1608,15 +1805,18 @@
           <t>MOVI3</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" t="n">
+        <v>64</v>
+      </c>
+      <c r="C66" t="inlineStr">
         <is>
           <t>Movida</t>
         </is>
       </c>
-      <c r="C66" t="n">
+      <c r="D66" t="n">
         <v>5821400</v>
       </c>
-      <c r="D66" t="n">
+      <c r="E66" t="n">
         <v>1449885568</v>
       </c>
     </row>
@@ -1626,15 +1826,18 @@
           <t>SIMH3</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" t="n">
+        <v>65</v>
+      </c>
+      <c r="C67" t="inlineStr">
         <is>
           <t>Simpar</t>
         </is>
       </c>
-      <c r="C67" t="n">
+      <c r="D67" t="n">
         <v>5803700</v>
       </c>
-      <c r="D67" t="n">
+      <c r="E67" t="n">
         <v>3118465280</v>
       </c>
     </row>
@@ -1644,15 +1847,18 @@
           <t>CPLE3</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" t="n">
+        <v>66</v>
+      </c>
+      <c r="C68" t="inlineStr">
         <is>
           <t>Copel</t>
         </is>
       </c>
-      <c r="C68" t="n">
+      <c r="D68" t="n">
         <v>5736600</v>
       </c>
-      <c r="D68" t="n">
+      <c r="E68" t="n">
         <v>29502402560</v>
       </c>
     </row>
@@ -1662,15 +1868,18 @@
           <t>EMBR3</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" t="n">
+        <v>67</v>
+      </c>
+      <c r="C69" t="inlineStr">
         <is>
           <t>Embraer</t>
         </is>
       </c>
-      <c r="C69" t="n">
+      <c r="D69" t="n">
         <v>5653000</v>
       </c>
-      <c r="D69" t="n">
+      <c r="E69" t="n">
         <v>55009316864</v>
       </c>
     </row>
@@ -1680,15 +1889,18 @@
           <t>VIVA3</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" t="n">
+        <v>68</v>
+      </c>
+      <c r="C70" t="inlineStr">
         <is>
           <t>Vivara</t>
         </is>
       </c>
-      <c r="C70" t="n">
+      <c r="D70" t="n">
         <v>5411200</v>
       </c>
-      <c r="D70" t="n">
+      <c r="E70" t="n">
         <v>4195910144</v>
       </c>
     </row>
@@ -1698,15 +1910,18 @@
           <t>CYRE3</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" t="n">
+        <v>69</v>
+      </c>
+      <c r="C71" t="inlineStr">
         <is>
           <t>Cyrela</t>
         </is>
       </c>
-      <c r="C71" t="n">
+      <c r="D71" t="n">
         <v>5257900</v>
       </c>
-      <c r="D71" t="n">
+      <c r="E71" t="n">
         <v>8432479744</v>
       </c>
     </row>
@@ -1716,15 +1931,18 @@
           <t>AMER3</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" t="n">
+        <v>70</v>
+      </c>
+      <c r="C72" t="inlineStr">
         <is>
           <t>Americanas</t>
         </is>
       </c>
-      <c r="C72" t="n">
+      <c r="D72" t="n">
         <v>4929000</v>
       </c>
-      <c r="D72" t="n">
+      <c r="E72" t="n">
         <v>1255529856</v>
       </c>
     </row>
@@ -1734,15 +1952,18 @@
           <t>ALOS3</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" t="n">
+        <v>71</v>
+      </c>
+      <c r="C73" t="inlineStr">
         <is>
           <t>Allos</t>
         </is>
       </c>
-      <c r="C73" t="n">
+      <c r="D73" t="n">
         <v>4896100</v>
       </c>
-      <c r="D73" t="n">
+      <c r="E73" t="n">
         <v>9584971776</v>
       </c>
     </row>
@@ -1752,15 +1973,18 @@
           <t>QUAL3</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" t="n">
+        <v>72</v>
+      </c>
+      <c r="C74" t="inlineStr">
         <is>
           <t>Qualicorp</t>
         </is>
       </c>
-      <c r="C74" t="n">
+      <c r="D74" t="n">
         <v>4838200</v>
       </c>
-      <c r="D74" t="n">
+      <c r="E74" t="n">
         <v>489503776</v>
       </c>
     </row>
@@ -1770,15 +1994,18 @@
           <t>ECOR3</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" t="n">
+        <v>73</v>
+      </c>
+      <c r="C75" t="inlineStr">
         <is>
           <t>EcoRodovias</t>
         </is>
       </c>
-      <c r="C75" t="n">
+      <c r="D75" t="n">
         <v>4657500</v>
       </c>
-      <c r="D75" t="n">
+      <c r="E75" t="n">
         <v>3860696576</v>
       </c>
     </row>
@@ -1788,15 +2015,18 @@
           <t>JBSS3</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" t="n">
+        <v>74</v>
+      </c>
+      <c r="C76" t="inlineStr">
         <is>
           <t>JBS</t>
         </is>
       </c>
-      <c r="C76" t="n">
+      <c r="D76" t="n">
         <v>4397200</v>
       </c>
-      <c r="D76" t="n">
+      <c r="E76" t="n">
         <v>73708126208</v>
       </c>
     </row>
@@ -1806,15 +2036,18 @@
           <t>RDOR3</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" t="n">
+        <v>75</v>
+      </c>
+      <c r="C77" t="inlineStr">
         <is>
           <t>Rede D'Or</t>
         </is>
       </c>
-      <c r="C77" t="n">
+      <c r="D77" t="n">
         <v>4332000</v>
       </c>
-      <c r="D77" t="n">
+      <c r="E77" t="n">
         <v>62643863552</v>
       </c>
     </row>
@@ -1824,15 +2057,18 @@
           <t>MRFG3</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" t="n">
+        <v>76</v>
+      </c>
+      <c r="C78" t="inlineStr">
         <is>
           <t>Marfrig</t>
         </is>
       </c>
-      <c r="C78" t="n">
+      <c r="D78" t="n">
         <v>4256200</v>
       </c>
-      <c r="D78" t="n">
+      <c r="E78" t="n">
         <v>13085999104</v>
       </c>
     </row>
@@ -1842,15 +2078,18 @@
           <t>SANB11</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" t="n">
+        <v>77</v>
+      </c>
+      <c r="C79" t="inlineStr">
         <is>
           <t>Banco Santander</t>
         </is>
       </c>
-      <c r="C79" t="n">
+      <c r="D79" t="n">
         <v>4210500</v>
       </c>
-      <c r="D79" t="n">
+      <c r="E79" t="n">
         <v>137883582464</v>
       </c>
     </row>
@@ -1860,15 +2099,18 @@
           <t>BBSE3</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" t="n">
+        <v>78</v>
+      </c>
+      <c r="C80" t="inlineStr">
         <is>
           <t>BB Seguridade</t>
         </is>
       </c>
-      <c r="C80" t="n">
+      <c r="D80" t="n">
         <v>4159500</v>
       </c>
-      <c r="D80" t="n">
+      <c r="E80" t="n">
         <v>77279576064</v>
       </c>
     </row>
@@ -1878,15 +2120,18 @@
           <t>SBSP3</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" t="n">
+        <v>80</v>
+      </c>
+      <c r="C81" t="inlineStr">
         <is>
           <t>Sabesp</t>
         </is>
       </c>
-      <c r="C81" t="n">
+      <c r="D81" t="n">
         <v>3892100</v>
       </c>
-      <c r="D81" t="n">
+      <c r="E81" t="n">
         <v>67872546816</v>
       </c>
     </row>
@@ -1896,15 +2141,18 @@
           <t>SRNA3</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" t="n">
+        <v>81</v>
+      </c>
+      <c r="C82" t="inlineStr">
         <is>
           <t>Serena Energia</t>
         </is>
       </c>
-      <c r="C82" t="n">
+      <c r="D82" t="n">
         <v>3826700</v>
       </c>
-      <c r="D82" t="n">
+      <c r="E82" t="n">
         <v>4800924672</v>
       </c>
     </row>
@@ -1914,15 +2162,18 @@
           <t>CEAB3</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" t="n">
+        <v>82</v>
+      </c>
+      <c r="C83" t="inlineStr">
         <is>
           <t>C&amp;A</t>
         </is>
       </c>
-      <c r="C83" t="n">
+      <c r="D83" t="n">
         <v>3811700</v>
       </c>
-      <c r="D83" t="n">
+      <c r="E83" t="n">
         <v>3241931008</v>
       </c>
     </row>
@@ -1932,15 +2183,18 @@
           <t>AZEV3</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" t="n">
+        <v>83</v>
+      </c>
+      <c r="C84" t="inlineStr">
         <is>
           <t>Azevedo &amp; Travassos</t>
         </is>
       </c>
-      <c r="C84" t="n">
+      <c r="D84" t="n">
         <v>3777200</v>
       </c>
-      <c r="D84" t="n">
+      <c r="E84" t="n">
         <v>578351360</v>
       </c>
     </row>
@@ -1950,15 +2204,18 @@
           <t>BRAP4</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" t="n">
+        <v>84</v>
+      </c>
+      <c r="C85" t="inlineStr">
         <is>
           <t>Bradespar</t>
         </is>
       </c>
-      <c r="C85" t="n">
+      <c r="D85" t="n">
         <v>3754000</v>
       </c>
-      <c r="D85" t="n">
+      <c r="E85" t="n">
         <v>6669442560</v>
       </c>
     </row>
@@ -1968,15 +2225,18 @@
           <t>CBAV3</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" t="n">
+        <v>85</v>
+      </c>
+      <c r="C86" t="inlineStr">
         <is>
           <t>CBA</t>
         </is>
       </c>
-      <c r="C86" t="n">
+      <c r="D86" t="n">
         <v>3744600</v>
       </c>
-      <c r="D86" t="n">
+      <c r="E86" t="n">
         <v>3248854272</v>
       </c>
     </row>
@@ -1986,15 +2246,18 @@
           <t>JHSF3</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" t="n">
+        <v>86</v>
+      </c>
+      <c r="C87" t="inlineStr">
         <is>
           <t>JHSF</t>
         </is>
       </c>
-      <c r="C87" t="n">
+      <c r="D87" t="n">
         <v>3659400</v>
       </c>
-      <c r="D87" t="n">
+      <c r="E87" t="n">
         <v>2629613056</v>
       </c>
     </row>
@@ -2004,15 +2267,18 @@
           <t>LJQQ3</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" t="n">
+        <v>87</v>
+      </c>
+      <c r="C88" t="inlineStr">
         <is>
           <t>Lojas Quero-Quero</t>
         </is>
       </c>
-      <c r="C88" t="n">
+      <c r="D88" t="n">
         <v>3640300</v>
       </c>
-      <c r="D88" t="n">
+      <c r="E88" t="n">
         <v>482116576</v>
       </c>
     </row>
@@ -2022,15 +2288,18 @@
           <t>BRKM5</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" t="n">
+        <v>88</v>
+      </c>
+      <c r="C89" t="inlineStr">
         <is>
           <t>Braskem</t>
         </is>
       </c>
-      <c r="C89" t="n">
+      <c r="D89" t="n">
         <v>3531100</v>
       </c>
-      <c r="D89" t="n">
+      <c r="E89" t="n">
         <v>8874245120</v>
       </c>
     </row>
@@ -2040,15 +2309,18 @@
           <t>YDUQ3</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" t="n">
+        <v>91</v>
+      </c>
+      <c r="C90" t="inlineStr">
         <is>
           <t>YDUQS</t>
         </is>
       </c>
-      <c r="C90" t="n">
+      <c r="D90" t="n">
         <v>3397800</v>
       </c>
-      <c r="D90" t="n">
+      <c r="E90" t="n">
         <v>2968377600</v>
       </c>
     </row>
@@ -2058,15 +2330,18 @@
           <t>TIMS3</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" t="n">
+        <v>92</v>
+      </c>
+      <c r="C91" t="inlineStr">
         <is>
           <t>TIM</t>
         </is>
       </c>
-      <c r="C91" t="n">
+      <c r="D91" t="n">
         <v>3385300</v>
       </c>
-      <c r="D91" t="n">
+      <c r="E91" t="n">
         <v>41895391232</v>
       </c>
     </row>
@@ -2076,15 +2351,18 @@
           <t>CXSE3</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" t="n">
+        <v>93</v>
+      </c>
+      <c r="C92" t="inlineStr">
         <is>
           <t>Caixa Seguridade</t>
         </is>
       </c>
-      <c r="C92" t="n">
+      <c r="D92" t="n">
         <v>3329200</v>
       </c>
-      <c r="D92" t="n">
+      <c r="E92" t="n">
         <v>47550001152</v>
       </c>
     </row>
@@ -2094,15 +2372,18 @@
           <t>PGMN3</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" t="n">
+        <v>94</v>
+      </c>
+      <c r="C93" t="inlineStr">
         <is>
           <t>Pague Menos</t>
         </is>
       </c>
-      <c r="C93" t="n">
+      <c r="D93" t="n">
         <v>3284100</v>
       </c>
-      <c r="D93" t="n">
+      <c r="E93" t="n">
         <v>1775971840</v>
       </c>
     </row>
@@ -2112,15 +2393,18 @@
           <t>EVEN3</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" t="n">
+        <v>95</v>
+      </c>
+      <c r="C94" t="inlineStr">
         <is>
           <t>Even</t>
         </is>
       </c>
-      <c r="C94" t="n">
+      <c r="D94" t="n">
         <v>3149800</v>
       </c>
-      <c r="D94" t="n">
+      <c r="E94" t="n">
         <v>1368149120</v>
       </c>
     </row>
@@ -2130,15 +2414,18 @@
           <t>KLBN11</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" t="n">
+        <v>96</v>
+      </c>
+      <c r="C95" t="inlineStr">
         <is>
           <t>Klabin</t>
         </is>
       </c>
-      <c r="C95" t="n">
+      <c r="D95" t="n">
         <v>3103700</v>
       </c>
-      <c r="D95" t="n">
+      <c r="E95" t="n">
         <v>128619708416</v>
       </c>
     </row>
@@ -2148,15 +2435,18 @@
           <t>ONCO3</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" t="n">
+        <v>97</v>
+      </c>
+      <c r="C96" t="inlineStr">
         <is>
           <t>Oncoclínicas</t>
         </is>
       </c>
-      <c r="C96" t="n">
+      <c r="D96" t="n">
         <v>3056100</v>
       </c>
-      <c r="D96" t="n">
+      <c r="E96" t="n">
         <v>3442394112</v>
       </c>
     </row>
@@ -2166,15 +2456,18 @@
           <t>SMFT3</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" t="n">
+        <v>98</v>
+      </c>
+      <c r="C97" t="inlineStr">
         <is>
           <t>Smart Fit</t>
         </is>
       </c>
-      <c r="C97" t="n">
+      <c r="D97" t="n">
         <v>3017900</v>
       </c>
-      <c r="D97" t="n">
+      <c r="E97" t="n">
         <v>11765825536</v>
       </c>
     </row>
@@ -2184,15 +2477,18 @@
           <t>CSMG3</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" t="n">
+        <v>99</v>
+      </c>
+      <c r="C98" t="inlineStr">
         <is>
           <t>COPASA</t>
         </is>
       </c>
-      <c r="C98" t="n">
+      <c r="D98" t="n">
         <v>2921400</v>
       </c>
-      <c r="D98" t="n">
+      <c r="E98" t="n">
         <v>9100343296</v>
       </c>
     </row>
@@ -2202,15 +2498,18 @@
           <t>CPFE3</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" t="n">
+        <v>100</v>
+      </c>
+      <c r="C99" t="inlineStr">
         <is>
           <t>CPFL Energia</t>
         </is>
       </c>
-      <c r="C99" t="n">
+      <c r="D99" t="n">
         <v>2901800</v>
       </c>
-      <c r="D99" t="n">
+      <c r="E99" t="n">
         <v>43140239360</v>
       </c>
     </row>
@@ -2220,15 +2519,18 @@
           <t>HYPE3</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" t="n">
+        <v>101</v>
+      </c>
+      <c r="C100" t="inlineStr">
         <is>
           <t>Hypera</t>
         </is>
       </c>
-      <c r="C100" t="n">
+      <c r="D100" t="n">
         <v>2825500</v>
       </c>
-      <c r="D100" t="n">
+      <c r="E100" t="n">
         <v>12846113792</v>
       </c>
     </row>
@@ -2238,15 +2540,18 @@
           <t>VIVT3</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" t="n">
+        <v>102</v>
+      </c>
+      <c r="C101" t="inlineStr">
         <is>
           <t>Vivo</t>
         </is>
       </c>
-      <c r="C101" t="n">
+      <c r="D101" t="n">
         <v>2810300</v>
       </c>
-      <c r="D101" t="n">
+      <c r="E101" t="n">
         <v>82932408320</v>
       </c>
     </row>
@@ -2256,15 +2561,18 @@
           <t>CLSA3</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" t="n">
+        <v>103</v>
+      </c>
+      <c r="C102" t="inlineStr">
         <is>
           <t>ClearSale</t>
         </is>
       </c>
-      <c r="C102" t="n">
+      <c r="D102" t="n">
         <v>2725300</v>
       </c>
-      <c r="D102" t="n">
+      <c r="E102" t="n">
         <v>1954217088</v>
       </c>
     </row>
@@ -2274,15 +2582,18 @@
           <t>GGPS3</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" t="n">
+        <v>104</v>
+      </c>
+      <c r="C103" t="inlineStr">
         <is>
           <t>GPS</t>
         </is>
       </c>
-      <c r="C103" t="n">
+      <c r="D103" t="n">
         <v>2660800</v>
       </c>
-      <c r="D103" t="n">
+      <c r="E103" t="n">
         <v>9711163392</v>
       </c>
     </row>
@@ -2292,15 +2603,18 @@
           <t>FLRY3</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" t="n">
+        <v>105</v>
+      </c>
+      <c r="C104" t="inlineStr">
         <is>
           <t>Fleury</t>
         </is>
       </c>
-      <c r="C104" t="n">
+      <c r="D104" t="n">
         <v>2656800</v>
       </c>
-      <c r="D104" t="n">
+      <c r="E104" t="n">
         <v>6294923264</v>
       </c>
     </row>
@@ -2310,15 +2624,18 @@
           <t>ENGI11</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" t="n">
+        <v>106</v>
+      </c>
+      <c r="C105" t="inlineStr">
         <is>
           <t>Energisa</t>
         </is>
       </c>
-      <c r="C105" t="n">
+      <c r="D105" t="n">
         <v>2635600</v>
       </c>
-      <c r="D105" t="n">
+      <c r="E105" t="n">
         <v>18710331392</v>
       </c>
     </row>
@@ -2328,15 +2645,18 @@
           <t>GMAT3</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" t="n">
+        <v>107</v>
+      </c>
+      <c r="C106" t="inlineStr">
         <is>
           <t>Grupo Mateus</t>
         </is>
       </c>
-      <c r="C106" t="n">
+      <c r="D106" t="n">
         <v>2595300</v>
       </c>
-      <c r="D106" t="n">
+      <c r="E106" t="n">
         <v>14484829184</v>
       </c>
     </row>
@@ -2346,15 +2666,18 @@
           <t>ALPA4</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B107" t="n">
+        <v>108</v>
+      </c>
+      <c r="C107" t="inlineStr">
         <is>
           <t>Alpargatas</t>
         </is>
       </c>
-      <c r="C107" t="n">
+      <c r="D107" t="n">
         <v>2439400</v>
       </c>
-      <c r="D107" t="n">
+      <c r="E107" t="n">
         <v>4706683392</v>
       </c>
     </row>
@@ -2364,15 +2687,18 @@
           <t>VVEO3</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" t="n">
+        <v>109</v>
+      </c>
+      <c r="C108" t="inlineStr">
         <is>
           <t>Viveo</t>
         </is>
       </c>
-      <c r="C108" t="n">
+      <c r="D108" t="n">
         <v>2407700</v>
       </c>
-      <c r="D108" t="n">
+      <c r="E108" t="n">
         <v>464237760</v>
       </c>
     </row>
@@ -2382,15 +2708,18 @@
           <t>ELET6</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B109" t="n">
+        <v>110</v>
+      </c>
+      <c r="C109" t="inlineStr">
         <is>
           <t>Eletrobras</t>
         </is>
       </c>
-      <c r="C109" t="n">
+      <c r="D109" t="n">
         <v>2369500</v>
       </c>
-      <c r="D109" t="n">
+      <c r="E109" t="n">
         <v>91713454080</v>
       </c>
     </row>
@@ -2400,15 +2729,18 @@
           <t>GOLL4</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B110" t="n">
+        <v>111</v>
+      </c>
+      <c r="C110" t="inlineStr">
         <is>
           <t>GOL</t>
         </is>
       </c>
-      <c r="C110" t="n">
+      <c r="D110" t="n">
         <v>2052800</v>
       </c>
-      <c r="D110" t="n">
+      <c r="E110" t="n">
         <v>4515200512</v>
       </c>
     </row>
@@ -2418,15 +2750,18 @@
           <t>ENJU3</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B111" t="n">
+        <v>112</v>
+      </c>
+      <c r="C111" t="inlineStr">
         <is>
           <t>Enjoei</t>
         </is>
       </c>
-      <c r="C111" t="n">
+      <c r="D111" t="n">
         <v>2007400</v>
       </c>
-      <c r="D111" t="n">
+      <c r="E111" t="n">
         <v>270623776</v>
       </c>
     </row>
@@ -2436,15 +2771,18 @@
           <t>DXCO3</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B112" t="n">
+        <v>113</v>
+      </c>
+      <c r="C112" t="inlineStr">
         <is>
           <t>Dexco</t>
         </is>
       </c>
-      <c r="C112" t="n">
+      <c r="D112" t="n">
         <v>1961200</v>
       </c>
-      <c r="D112" t="n">
+      <c r="E112" t="n">
         <v>4518760448</v>
       </c>
     </row>
@@ -2454,15 +2792,18 @@
           <t>HBSA3</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B113" t="n">
+        <v>114</v>
+      </c>
+      <c r="C113" t="inlineStr">
         <is>
           <t>Hidrovias do Brasil</t>
         </is>
       </c>
-      <c r="C113" t="n">
+      <c r="D113" t="n">
         <v>1944900</v>
       </c>
-      <c r="D113" t="n">
+      <c r="E113" t="n">
         <v>1805490560</v>
       </c>
     </row>
@@ -2472,15 +2813,18 @@
           <t>KEPL3</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B114" t="n">
+        <v>115</v>
+      </c>
+      <c r="C114" t="inlineStr">
         <is>
           <t>Kepler Weber</t>
         </is>
       </c>
-      <c r="C114" t="n">
+      <c r="D114" t="n">
         <v>1940400</v>
       </c>
-      <c r="D114" t="n">
+      <c r="E114" t="n">
         <v>1353223040</v>
       </c>
     </row>
@@ -2490,15 +2834,18 @@
           <t>PTBL3</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B115" t="n">
+        <v>116</v>
+      </c>
+      <c r="C115" t="inlineStr">
         <is>
           <t>Portobello</t>
         </is>
       </c>
-      <c r="C115" t="n">
+      <c r="D115" t="n">
         <v>1929800</v>
       </c>
-      <c r="D115" t="n">
+      <c r="E115" t="n">
         <v>493454528</v>
       </c>
     </row>
@@ -2508,15 +2855,18 @@
           <t>GFSA3</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B116" t="n">
+        <v>117</v>
+      </c>
+      <c r="C116" t="inlineStr">
         <is>
           <t>Gafisa</t>
         </is>
       </c>
-      <c r="C116" t="n">
+      <c r="D116" t="n">
         <v>1915700</v>
       </c>
-      <c r="D116" t="n">
+      <c r="E116" t="n">
         <v>106397192</v>
       </c>
     </row>
@@ -2526,15 +2876,18 @@
           <t>SBFG3</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B117" t="n">
+        <v>118</v>
+      </c>
+      <c r="C117" t="inlineStr">
         <is>
           <t>Grupo SBF</t>
         </is>
       </c>
-      <c r="C117" t="n">
+      <c r="D117" t="n">
         <v>1884500</v>
       </c>
-      <c r="D117" t="n">
+      <c r="E117" t="n">
         <v>2601059328</v>
       </c>
     </row>
@@ -2544,15 +2897,18 @@
           <t>RAPT4</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B118" t="n">
+        <v>119</v>
+      </c>
+      <c r="C118" t="inlineStr">
         <is>
           <t>Randon</t>
         </is>
       </c>
-      <c r="C118" t="n">
+      <c r="D118" t="n">
         <v>1877300</v>
       </c>
-      <c r="D118" t="n">
+      <c r="E118" t="n">
         <v>2984699648</v>
       </c>
     </row>
@@ -2562,15 +2918,18 @@
           <t>MYPK3</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B119" t="n">
+        <v>120</v>
+      </c>
+      <c r="C119" t="inlineStr">
         <is>
           <t>Iochpe-Maxion</t>
         </is>
       </c>
-      <c r="C119" t="n">
+      <c r="D119" t="n">
         <v>1875800</v>
       </c>
-      <c r="D119" t="n">
+      <c r="E119" t="n">
         <v>2041365120</v>
       </c>
     </row>
@@ -2580,15 +2939,18 @@
           <t>OIBR3</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B120" t="n">
+        <v>121</v>
+      </c>
+      <c r="C120" t="inlineStr">
         <is>
           <t>Oi</t>
         </is>
       </c>
-      <c r="C120" t="n">
+      <c r="D120" t="n">
         <v>1838700</v>
       </c>
-      <c r="D120" t="n">
+      <c r="E120" t="n">
         <v>396229568</v>
       </c>
     </row>
@@ -2598,15 +2960,18 @@
           <t>ISAE4</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B121" t="n">
+        <v>122</v>
+      </c>
+      <c r="C121" t="inlineStr">
         <is>
           <t>ISA Energia</t>
         </is>
       </c>
-      <c r="C121" t="n">
+      <c r="D121" t="n">
         <v>1834700</v>
       </c>
-      <c r="D121" t="n">
+      <c r="E121" t="n">
         <v>17129297920</v>
       </c>
     </row>
@@ -2616,15 +2981,18 @@
           <t>TAEE11</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B122" t="n">
+        <v>123</v>
+      </c>
+      <c r="C122" t="inlineStr">
         <is>
           <t>Taesa</t>
         </is>
       </c>
-      <c r="C122" t="n">
+      <c r="D122" t="n">
         <v>1794800</v>
       </c>
-      <c r="D122" t="n">
+      <c r="E122" t="n">
         <v>11737080832</v>
       </c>
     </row>
@@ -2634,15 +3002,18 @@
           <t>MTRE3</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B123" t="n">
+        <v>124</v>
+      </c>
+      <c r="C123" t="inlineStr">
         <is>
           <t>Mitre Realty</t>
         </is>
       </c>
-      <c r="C123" t="n">
+      <c r="D123" t="n">
         <v>1651700</v>
       </c>
-      <c r="D123" t="n">
+      <c r="E123" t="n">
         <v>352230752</v>
       </c>
     </row>
@@ -2652,15 +3023,18 @@
           <t>RECV3</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B124" t="n">
+        <v>125</v>
+      </c>
+      <c r="C124" t="inlineStr">
         <is>
           <t>PetroRecôncavo</t>
         </is>
       </c>
-      <c r="C124" t="n">
+      <c r="D124" t="n">
         <v>1612600</v>
       </c>
-      <c r="D124" t="n">
+      <c r="E124" t="n">
         <v>4792496128</v>
       </c>
     </row>
@@ -2670,15 +3044,18 @@
           <t>KLBN4</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B125" t="n">
+        <v>126</v>
+      </c>
+      <c r="C125" t="inlineStr">
         <is>
           <t>Klabin</t>
         </is>
       </c>
-      <c r="C125" t="n">
+      <c r="D125" t="n">
         <v>1564800</v>
       </c>
-      <c r="D125" t="n">
+      <c r="E125" t="n">
         <v>23981568000</v>
       </c>
     </row>
@@ -2688,15 +3065,18 @@
           <t>BRSR6</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B126" t="n">
+        <v>127</v>
+      </c>
+      <c r="C126" t="inlineStr">
         <is>
           <t>Banrisul</t>
         </is>
       </c>
-      <c r="C126" t="n">
+      <c r="D126" t="n">
         <v>1529300</v>
       </c>
-      <c r="D126" t="n">
+      <c r="E126" t="n">
         <v>4810818560</v>
       </c>
     </row>
@@ -2706,15 +3086,18 @@
           <t>DIRR3</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B127" t="n">
+        <v>128</v>
+      </c>
+      <c r="C127" t="inlineStr">
         <is>
           <t>Direcional</t>
         </is>
       </c>
-      <c r="C127" t="n">
+      <c r="D127" t="n">
         <v>1453200</v>
       </c>
-      <c r="D127" t="n">
+      <c r="E127" t="n">
         <v>5204250112</v>
       </c>
     </row>
@@ -2724,15 +3107,18 @@
           <t>PORT3</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B128" t="n">
+        <v>129</v>
+      </c>
+      <c r="C128" t="inlineStr">
         <is>
           <t>Wilson Sons</t>
         </is>
       </c>
-      <c r="C128" t="n">
+      <c r="D128" t="n">
         <v>1440200</v>
       </c>
-      <c r="D128" t="n">
+      <c r="E128" t="n">
         <v>7650968064</v>
       </c>
     </row>
@@ -2742,15 +3128,18 @@
           <t>PSSA3</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B129" t="n">
+        <v>130</v>
+      </c>
+      <c r="C129" t="inlineStr">
         <is>
           <t>Porto Seguro</t>
         </is>
       </c>
-      <c r="C129" t="n">
+      <c r="D129" t="n">
         <v>1422200</v>
       </c>
-      <c r="D129" t="n">
+      <c r="E129" t="n">
         <v>24942645248</v>
       </c>
     </row>
@@ -2760,15 +3149,18 @@
           <t>JSLG3</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B130" t="n">
+        <v>131</v>
+      </c>
+      <c r="C130" t="inlineStr">
         <is>
           <t>JSL</t>
         </is>
       </c>
-      <c r="C130" t="n">
+      <c r="D130" t="n">
         <v>1327200</v>
       </c>
-      <c r="D130" t="n">
+      <c r="E130" t="n">
         <v>1547239424</v>
       </c>
     </row>
@@ -2778,15 +3170,18 @@
           <t>IRBR3</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B131" t="n">
+        <v>132</v>
+      </c>
+      <c r="C131" t="inlineStr">
         <is>
           <t>IRB Brasil RE</t>
         </is>
       </c>
-      <c r="C131" t="n">
+      <c r="D131" t="n">
         <v>1295500</v>
       </c>
-      <c r="D131" t="n">
+      <c r="E131" t="n">
         <v>3972654336</v>
       </c>
     </row>
@@ -2796,15 +3191,18 @@
           <t>SAPR4</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B132" t="n">
+        <v>133</v>
+      </c>
+      <c r="C132" t="inlineStr">
         <is>
           <t>Sanepar</t>
         </is>
       </c>
-      <c r="C132" t="n">
+      <c r="D132" t="n">
         <v>1295100</v>
       </c>
-      <c r="D132" t="n">
+      <c r="E132" t="n">
         <v>8442616320</v>
       </c>
     </row>
@@ -2814,15 +3212,18 @@
           <t>PLPL3</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B133" t="n">
+        <v>134</v>
+      </c>
+      <c r="C133" t="inlineStr">
         <is>
           <t>Plano&amp;Plano</t>
         </is>
       </c>
-      <c r="C133" t="n">
+      <c r="D133" t="n">
         <v>1272200</v>
       </c>
-      <c r="D133" t="n">
+      <c r="E133" t="n">
         <v>2183929600</v>
       </c>
     </row>
@@ -2832,15 +3233,18 @@
           <t>CAML3</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B134" t="n">
+        <v>135</v>
+      </c>
+      <c r="C134" t="inlineStr">
         <is>
           <t>Camil Alimentos</t>
         </is>
       </c>
-      <c r="C134" t="n">
+      <c r="D134" t="n">
         <v>1243600</v>
       </c>
-      <c r="D134" t="n">
+      <c r="E134" t="n">
         <v>1296069760</v>
       </c>
     </row>
@@ -2850,15 +3254,18 @@
           <t>MLAS3</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B135" t="n">
+        <v>136</v>
+      </c>
+      <c r="C135" t="inlineStr">
         <is>
           <t>Multilaser</t>
         </is>
       </c>
-      <c r="C135" t="n">
+      <c r="D135" t="n">
         <v>1193700</v>
       </c>
-      <c r="D135" t="n">
+      <c r="E135" t="n">
         <v>976969728</v>
       </c>
     </row>
@@ -2868,15 +3275,18 @@
           <t>MEAL3</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B136" t="n">
+        <v>137</v>
+      </c>
+      <c r="C136" t="inlineStr">
         <is>
           <t>IMC Alimentação</t>
         </is>
       </c>
-      <c r="C136" t="n">
+      <c r="D136" t="n">
         <v>1183600</v>
       </c>
-      <c r="D136" t="n">
+      <c r="E136" t="n">
         <v>313987328</v>
       </c>
     </row>
@@ -2886,15 +3296,18 @@
           <t>ALUP11</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B137" t="n">
+        <v>138</v>
+      </c>
+      <c r="C137" t="inlineStr">
         <is>
           <t>Alupar</t>
         </is>
       </c>
-      <c r="C137" t="n">
+      <c r="D137" t="n">
         <v>1171200</v>
       </c>
-      <c r="D137" t="n">
+      <c r="E137" t="n">
         <v>14478958592</v>
       </c>
     </row>
@@ -2904,15 +3317,18 @@
           <t>VLID3</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B138" t="n">
+        <v>139</v>
+      </c>
+      <c r="C138" t="inlineStr">
         <is>
           <t>Valid</t>
         </is>
       </c>
-      <c r="C138" t="n">
+      <c r="D138" t="n">
         <v>1165700</v>
       </c>
-      <c r="D138" t="n">
+      <c r="E138" t="n">
         <v>1852208768</v>
       </c>
     </row>
@@ -2922,15 +3338,18 @@
           <t>CURY3</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B139" t="n">
+        <v>140</v>
+      </c>
+      <c r="C139" t="inlineStr">
         <is>
           <t>Cury</t>
         </is>
       </c>
-      <c r="C139" t="n">
+      <c r="D139" t="n">
         <v>1164300</v>
       </c>
-      <c r="D139" t="n">
+      <c r="E139" t="n">
         <v>6762993664</v>
       </c>
     </row>
@@ -2940,15 +3359,18 @@
           <t>BPAN4</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B140" t="n">
+        <v>142</v>
+      </c>
+      <c r="C140" t="inlineStr">
         <is>
           <t>Banco Pan</t>
         </is>
       </c>
-      <c r="C140" t="n">
+      <c r="D140" t="n">
         <v>1142100</v>
       </c>
-      <c r="D140" t="n">
+      <c r="E140" t="n">
         <v>9016609792</v>
       </c>
     </row>
@@ -2958,15 +3380,18 @@
           <t>GRND3</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B141" t="n">
+        <v>143</v>
+      </c>
+      <c r="C141" t="inlineStr">
         <is>
           <t>Grendene</t>
         </is>
       </c>
-      <c r="C141" t="n">
+      <c r="D141" t="n">
         <v>1107600</v>
       </c>
-      <c r="D141" t="n">
+      <c r="E141" t="n">
         <v>5245467136</v>
       </c>
     </row>
@@ -2976,15 +3401,18 @@
           <t>GUAR3</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B142" t="n">
+        <v>144</v>
+      </c>
+      <c r="C142" t="inlineStr">
         <is>
           <t>Guararapes</t>
         </is>
       </c>
-      <c r="C142" t="n">
+      <c r="D142" t="n">
         <v>1089600</v>
       </c>
-      <c r="D142" t="n">
+      <c r="E142" t="n">
         <v>3694057728</v>
       </c>
     </row>
@@ -2994,15 +3422,18 @@
           <t>POSI3</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B143" t="n">
+        <v>145</v>
+      </c>
+      <c r="C143" t="inlineStr">
         <is>
           <t>Positivo</t>
         </is>
       </c>
-      <c r="C143" t="n">
+      <c r="D143" t="n">
         <v>1086400</v>
       </c>
-      <c r="D143" t="n">
+      <c r="E143" t="n">
         <v>750354048</v>
       </c>
     </row>
@@ -3012,15 +3443,18 @@
           <t>EGIE3</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B144" t="n">
+        <v>146</v>
+      </c>
+      <c r="C144" t="inlineStr">
         <is>
           <t>Engie</t>
         </is>
       </c>
-      <c r="C144" t="n">
+      <c r="D144" t="n">
         <v>1063300</v>
       </c>
-      <c r="D144" t="n">
+      <c r="E144" t="n">
         <v>30817601536</v>
       </c>
     </row>
@@ -3030,15 +3464,18 @@
           <t>DASA3</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="B145" t="n">
+        <v>147</v>
+      </c>
+      <c r="C145" t="inlineStr">
         <is>
           <t>Dasa</t>
         </is>
       </c>
-      <c r="C145" t="n">
+      <c r="D145" t="n">
         <v>1034200</v>
       </c>
-      <c r="D145" t="n">
+      <c r="E145" t="n">
         <v>2374334976</v>
       </c>
     </row>
@@ -3048,15 +3485,18 @@
           <t>ZAMP3</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
+      <c r="B146" t="n">
+        <v>148</v>
+      </c>
+      <c r="C146" t="inlineStr">
         <is>
           <t>Zamp</t>
         </is>
       </c>
-      <c r="C146" t="n">
+      <c r="D146" t="n">
         <v>1032700</v>
       </c>
-      <c r="D146" t="n">
+      <c r="E146" t="n">
         <v>1116953600</v>
       </c>
     </row>
@@ -3066,15 +3506,18 @@
           <t>TRIS3</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="B147" t="n">
+        <v>149</v>
+      </c>
+      <c r="C147" t="inlineStr">
         <is>
           <t>Trisul</t>
         </is>
       </c>
-      <c r="C147" t="n">
+      <c r="D147" t="n">
         <v>1020200</v>
       </c>
-      <c r="D147" t="n">
+      <c r="E147" t="n">
         <v>1154943744</v>
       </c>
     </row>
@@ -3084,15 +3527,18 @@
           <t>FESA4</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="B148" t="n">
+        <v>150</v>
+      </c>
+      <c r="C148" t="inlineStr">
         <is>
           <t>Ferbasa</t>
         </is>
       </c>
-      <c r="C148" t="n">
+      <c r="D148" t="n">
         <v>983500</v>
       </c>
-      <c r="D148" t="n">
+      <c r="E148" t="n">
         <v>3052506624</v>
       </c>
     </row>
@@ -3102,15 +3548,18 @@
           <t>ITUB3</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="B149" t="n">
+        <v>151</v>
+      </c>
+      <c r="C149" t="inlineStr">
         <is>
           <t>Itaú Unibanco</t>
         </is>
       </c>
-      <c r="C149" t="n">
+      <c r="D149" t="n">
         <v>969700</v>
       </c>
-      <c r="D149" t="n">
+      <c r="E149" t="n">
         <v>317262200832</v>
       </c>
     </row>
@@ -3120,15 +3569,18 @@
           <t>TTEN3</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="B150" t="n">
+        <v>152</v>
+      </c>
+      <c r="C150" t="inlineStr">
         <is>
           <t>3tentos</t>
         </is>
       </c>
-      <c r="C150" t="n">
+      <c r="D150" t="n">
         <v>941700</v>
       </c>
-      <c r="D150" t="n">
+      <c r="E150" t="n">
         <v>7042568704</v>
       </c>
     </row>
@@ -3138,15 +3590,18 @@
           <t>SAPR11</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B151" t="n">
+        <v>153</v>
+      </c>
+      <c r="C151" t="inlineStr">
         <is>
           <t>Sanepar</t>
         </is>
       </c>
-      <c r="C151" t="n">
+      <c r="D151" t="n">
         <v>937800</v>
       </c>
-      <c r="D151" t="n">
+      <c r="E151" t="n">
         <v>8399277568</v>
       </c>
     </row>
@@ -3156,15 +3611,18 @@
           <t>ARML3</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="B152" t="n">
+        <v>154</v>
+      </c>
+      <c r="C152" t="inlineStr">
         <is>
           <t>Armac</t>
         </is>
       </c>
-      <c r="C152" t="n">
+      <c r="D152" t="n">
         <v>933800</v>
       </c>
-      <c r="D152" t="n">
+      <c r="E152" t="n">
         <v>1599208320</v>
       </c>
     </row>
@@ -3174,15 +3632,18 @@
           <t>SMTO3</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="B153" t="n">
+        <v>155</v>
+      </c>
+      <c r="C153" t="inlineStr">
         <is>
           <t>São Martinho</t>
         </is>
       </c>
-      <c r="C153" t="n">
+      <c r="D153" t="n">
         <v>933600</v>
       </c>
-      <c r="D153" t="n">
+      <c r="E153" t="n">
         <v>7294431744</v>
       </c>
     </row>
@@ -3192,15 +3653,18 @@
           <t>PRNR3</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B154" t="n">
+        <v>156</v>
+      </c>
+      <c r="C154" t="inlineStr">
         <is>
           <t>Priner</t>
         </is>
       </c>
-      <c r="C154" t="n">
+      <c r="D154" t="n">
         <v>903500</v>
       </c>
-      <c r="D154" t="n">
+      <c r="E154" t="n">
         <v>815278016</v>
       </c>
     </row>
@@ -3210,15 +3674,18 @@
           <t>DESK3</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B155" t="n">
+        <v>157</v>
+      </c>
+      <c r="C155" t="inlineStr">
         <is>
           <t>Desktop</t>
         </is>
       </c>
-      <c r="C155" t="n">
+      <c r="D155" t="n">
         <v>867900</v>
       </c>
-      <c r="D155" t="n">
+      <c r="E155" t="n">
         <v>970493952</v>
       </c>
     </row>
@@ -3228,15 +3695,18 @@
           <t>TFCO4</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B156" t="n">
+        <v>158</v>
+      </c>
+      <c r="C156" t="inlineStr">
         <is>
           <t>Track &amp; Field</t>
         </is>
       </c>
-      <c r="C156" t="n">
+      <c r="D156" t="n">
         <v>864200</v>
       </c>
-      <c r="D156" t="n">
+      <c r="E156" t="n">
         <v>1507601920</v>
       </c>
     </row>
@@ -3246,15 +3716,18 @@
           <t>NEOE3</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B157" t="n">
+        <v>159</v>
+      </c>
+      <c r="C157" t="inlineStr">
         <is>
           <t>Neoenergia</t>
         </is>
       </c>
-      <c r="C157" t="n">
+      <c r="D157" t="n">
         <v>851100</v>
       </c>
-      <c r="D157" t="n">
+      <c r="E157" t="n">
         <v>25052829696</v>
       </c>
     </row>
@@ -3264,15 +3737,18 @@
           <t>VULC3</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B158" t="n">
+        <v>160</v>
+      </c>
+      <c r="C158" t="inlineStr">
         <is>
           <t>Vulcabras</t>
         </is>
       </c>
-      <c r="C158" t="n">
+      <c r="D158" t="n">
         <v>837500</v>
       </c>
-      <c r="D158" t="n">
+      <c r="E158" t="n">
         <v>4332592128</v>
       </c>
     </row>
@@ -3282,15 +3758,18 @@
           <t>ODPV3</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B159" t="n">
+        <v>161</v>
+      </c>
+      <c r="C159" t="inlineStr">
         <is>
           <t>Odontoprev</t>
         </is>
       </c>
-      <c r="C159" t="n">
+      <c r="D159" t="n">
         <v>837200</v>
       </c>
-      <c r="D159" t="n">
+      <c r="E159" t="n">
         <v>5965867520</v>
       </c>
     </row>
@@ -3300,15 +3779,18 @@
           <t>ESPA3</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="B160" t="n">
+        <v>162</v>
+      </c>
+      <c r="C160" t="inlineStr">
         <is>
           <t>Espaçolaser</t>
         </is>
       </c>
-      <c r="C160" t="n">
+      <c r="D160" t="n">
         <v>790800</v>
       </c>
-      <c r="D160" t="n">
+      <c r="E160" t="n">
         <v>256610320</v>
       </c>
     </row>
@@ -3318,15 +3800,18 @@
           <t>ABCB4</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
+      <c r="B161" t="n">
+        <v>163</v>
+      </c>
+      <c r="C161" t="inlineStr">
         <is>
           <t>Banco ABC Brasil</t>
         </is>
       </c>
-      <c r="C161" t="n">
+      <c r="D161" t="n">
         <v>761900</v>
       </c>
-      <c r="D161" t="n">
+      <c r="E161" t="n">
         <v>5012994048</v>
       </c>
     </row>
@@ -3336,15 +3821,18 @@
           <t>SEQL3</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
+      <c r="B162" t="n">
+        <v>164</v>
+      </c>
+      <c r="C162" t="inlineStr">
         <is>
           <t>Sequoia Logística</t>
         </is>
       </c>
-      <c r="C162" t="n">
+      <c r="D162" t="n">
         <v>750800</v>
       </c>
-      <c r="D162" t="n">
+      <c r="E162" t="n">
         <v>72718464</v>
       </c>
     </row>
@@ -3354,15 +3842,18 @@
           <t>UNIP6</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="B163" t="n">
+        <v>165</v>
+      </c>
+      <c r="C163" t="inlineStr">
         <is>
           <t>Unipar</t>
         </is>
       </c>
-      <c r="C163" t="n">
+      <c r="D163" t="n">
         <v>712800</v>
       </c>
-      <c r="D163" t="n">
+      <c r="E163" t="n">
         <v>5892864512</v>
       </c>
     </row>
@@ -3372,15 +3863,18 @@
           <t>RCSL3</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="B164" t="n">
+        <v>166</v>
+      </c>
+      <c r="C164" t="inlineStr">
         <is>
           <t>Recrusul</t>
         </is>
       </c>
-      <c r="C164" t="n">
+      <c r="D164" t="n">
         <v>674600</v>
       </c>
-      <c r="D164" t="n">
+      <c r="E164" t="n">
         <v>56354256</v>
       </c>
     </row>
@@ -3390,15 +3884,18 @@
           <t>CASH3</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="B165" t="n">
+        <v>167</v>
+      </c>
+      <c r="C165" t="inlineStr">
         <is>
           <t>Méliuz</t>
         </is>
       </c>
-      <c r="C165" t="n">
+      <c r="D165" t="n">
         <v>641800</v>
       </c>
-      <c r="D165" t="n">
+      <c r="E165" t="n">
         <v>311194368</v>
       </c>
     </row>
@@ -3408,15 +3905,18 @@
           <t>OPCT3</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
+      <c r="B166" t="n">
+        <v>168</v>
+      </c>
+      <c r="C166" t="inlineStr">
         <is>
           <t>OceanPact</t>
         </is>
       </c>
-      <c r="C166" t="n">
+      <c r="D166" t="n">
         <v>633600</v>
       </c>
-      <c r="D166" t="n">
+      <c r="E166" t="n">
         <v>1070701248</v>
       </c>
     </row>
@@ -3426,15 +3926,18 @@
           <t>MILS3</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
+      <c r="B167" t="n">
+        <v>169</v>
+      </c>
+      <c r="C167" t="inlineStr">
         <is>
           <t>Mills</t>
         </is>
       </c>
-      <c r="C167" t="n">
+      <c r="D167" t="n">
         <v>610400</v>
       </c>
-      <c r="D167" t="n">
+      <c r="E167" t="n">
         <v>2140621312</v>
       </c>
     </row>
@@ -3444,15 +3947,18 @@
           <t>LAVV3</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
+      <c r="B168" t="n">
+        <v>170</v>
+      </c>
+      <c r="C168" t="inlineStr">
         <is>
           <t>Lavvi Incorporadora</t>
         </is>
       </c>
-      <c r="C168" t="n">
+      <c r="D168" t="n">
         <v>558000</v>
       </c>
-      <c r="D168" t="n">
+      <c r="E168" t="n">
         <v>1850760064</v>
       </c>
     </row>
@@ -3462,15 +3968,18 @@
           <t>MDNE3</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
+      <c r="B169" t="n">
+        <v>171</v>
+      </c>
+      <c r="C169" t="inlineStr">
         <is>
           <t>Moura Dubeux</t>
         </is>
       </c>
-      <c r="C169" t="n">
+      <c r="D169" t="n">
         <v>556400</v>
       </c>
-      <c r="D169" t="n">
+      <c r="E169" t="n">
         <v>1101306752</v>
       </c>
     </row>
@@ -3480,15 +3989,18 @@
           <t>SHUL4</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="B170" t="n">
+        <v>172</v>
+      </c>
+      <c r="C170" t="inlineStr">
         <is>
           <t>Schulz</t>
         </is>
       </c>
-      <c r="C170" t="n">
+      <c r="D170" t="n">
         <v>526900</v>
       </c>
-      <c r="D170" t="n">
+      <c r="E170" t="n">
         <v>1189951488</v>
       </c>
     </row>
@@ -3498,15 +4010,18 @@
           <t>HBRE3</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="B171" t="n">
+        <v>173</v>
+      </c>
+      <c r="C171" t="inlineStr">
         <is>
           <t>HBR Realty</t>
         </is>
       </c>
-      <c r="C171" t="n">
+      <c r="D171" t="n">
         <v>526400</v>
       </c>
-      <c r="D171" t="n">
+      <c r="E171" t="n">
         <v>308703008</v>
       </c>
     </row>
@@ -3516,15 +4031,18 @@
           <t>MELK3</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B172" t="n">
+        <v>174</v>
+      </c>
+      <c r="C172" t="inlineStr">
         <is>
           <t>Melnick</t>
         </is>
       </c>
-      <c r="C172" t="n">
+      <c r="D172" t="n">
         <v>508600</v>
       </c>
-      <c r="D172" t="n">
+      <c r="E172" t="n">
         <v>815045312</v>
       </c>
     </row>
@@ -3534,15 +4052,18 @@
           <t>MBLY3</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="B173" t="n">
+        <v>175</v>
+      </c>
+      <c r="C173" t="inlineStr">
         <is>
           <t>Mobly</t>
         </is>
       </c>
-      <c r="C173" t="n">
+      <c r="D173" t="n">
         <v>507900</v>
       </c>
-      <c r="D173" t="n">
+      <c r="E173" t="n">
         <v>147315600</v>
       </c>
     </row>
@@ -3552,15 +4073,18 @@
           <t>SEER3</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B174" t="n">
+        <v>176</v>
+      </c>
+      <c r="C174" t="inlineStr">
         <is>
           <t>Ser Educacional</t>
         </is>
       </c>
-      <c r="C174" t="n">
+      <c r="D174" t="n">
         <v>503800</v>
       </c>
-      <c r="D174" t="n">
+      <c r="E174" t="n">
         <v>559790016</v>
       </c>
     </row>
@@ -3570,15 +4094,18 @@
           <t>JALL3</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B175" t="n">
+        <v>177</v>
+      </c>
+      <c r="C175" t="inlineStr">
         <is>
           <t>Jalles Machado</t>
         </is>
       </c>
-      <c r="C175" t="n">
+      <c r="D175" t="n">
         <v>494700</v>
       </c>
-      <c r="D175" t="n">
+      <c r="E175" t="n">
         <v>1236346752</v>
       </c>
     </row>
@@ -3588,15 +4115,18 @@
           <t>MATD3</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B176" t="n">
+        <v>178</v>
+      </c>
+      <c r="C176" t="inlineStr">
         <is>
           <t>Mater Dei</t>
         </is>
       </c>
-      <c r="C176" t="n">
+      <c r="D176" t="n">
         <v>487300</v>
       </c>
-      <c r="D176" t="n">
+      <c r="E176" t="n">
         <v>1426952832</v>
       </c>
     </row>
@@ -3606,15 +4136,18 @@
           <t>WIZC3</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B177" t="n">
+        <v>179</v>
+      </c>
+      <c r="C177" t="inlineStr">
         <is>
           <t>Wiz Soluções</t>
         </is>
       </c>
-      <c r="C177" t="n">
+      <c r="D177" t="n">
         <v>479800</v>
       </c>
-      <c r="D177" t="n">
+      <c r="E177" t="n">
         <v>989824384</v>
       </c>
     </row>
@@ -3624,15 +4157,18 @@
           <t>CSED3</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="B178" t="n">
+        <v>180</v>
+      </c>
+      <c r="C178" t="inlineStr">
         <is>
           <t>Cruzeiro do Sul Educacional</t>
         </is>
       </c>
-      <c r="C178" t="n">
+      <c r="D178" t="n">
         <v>469900</v>
       </c>
-      <c r="D178" t="n">
+      <c r="E178" t="n">
         <v>1341518336</v>
       </c>
     </row>
@@ -3642,15 +4178,18 @@
           <t>MDIA3</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="B179" t="n">
+        <v>181</v>
+      </c>
+      <c r="C179" t="inlineStr">
         <is>
           <t>M. Dias Branco</t>
         </is>
       </c>
-      <c r="C179" t="n">
+      <c r="D179" t="n">
         <v>447000</v>
       </c>
-      <c r="D179" t="n">
+      <c r="E179" t="n">
         <v>7807437312</v>
       </c>
     </row>
@@ -3660,15 +4199,18 @@
           <t>VTRU3</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="B180" t="n">
+        <v>182</v>
+      </c>
+      <c r="C180" t="inlineStr">
         <is>
           <t>VITRUBREPCOM</t>
         </is>
       </c>
-      <c r="C180" t="n">
+      <c r="D180" t="n">
         <v>438500</v>
       </c>
-      <c r="D180" t="n">
+      <c r="E180" t="n">
         <v>846048768</v>
       </c>
     </row>
@@ -3678,15 +4220,18 @@
           <t>HBOR3</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B181" t="n">
+        <v>183</v>
+      </c>
+      <c r="C181" t="inlineStr">
         <is>
           <t>Helbor</t>
         </is>
       </c>
-      <c r="C181" t="n">
+      <c r="D181" t="n">
         <v>420600</v>
       </c>
-      <c r="D181" t="n">
+      <c r="E181" t="n">
         <v>226906752</v>
       </c>
     </row>
@@ -3696,15 +4241,18 @@
           <t>ORVR3</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B182" t="n">
+        <v>184</v>
+      </c>
+      <c r="C182" t="inlineStr">
         <is>
           <t>Orizon</t>
         </is>
       </c>
-      <c r="C182" t="n">
+      <c r="D182" t="n">
         <v>415600</v>
       </c>
-      <c r="D182" t="n">
+      <c r="E182" t="n">
         <v>3620806656</v>
       </c>
     </row>
@@ -3714,15 +4262,18 @@
           <t>AMAR3</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B183" t="n">
+        <v>185</v>
+      </c>
+      <c r="C183" t="inlineStr">
         <is>
           <t>Lojas Marisa</t>
         </is>
       </c>
-      <c r="C183" t="n">
+      <c r="D183" t="n">
         <v>405400</v>
       </c>
-      <c r="D183" t="n">
+      <c r="E183" t="n">
         <v>816374400</v>
       </c>
     </row>
@@ -3732,15 +4283,18 @@
           <t>SYNE3</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="B184" t="n">
+        <v>186</v>
+      </c>
+      <c r="C184" t="inlineStr">
         <is>
           <t>SYN</t>
         </is>
       </c>
-      <c r="C184" t="n">
+      <c r="D184" t="n">
         <v>404000</v>
       </c>
-      <c r="D184" t="n">
+      <c r="E184" t="n">
         <v>740323392</v>
       </c>
     </row>
@@ -3750,15 +4304,18 @@
           <t>AERI3</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B185" t="n">
+        <v>187</v>
+      </c>
+      <c r="C185" t="inlineStr">
         <is>
           <t>Aeris Energy</t>
         </is>
       </c>
-      <c r="C185" t="n">
+      <c r="D185" t="n">
         <v>399400</v>
       </c>
-      <c r="D185" t="n">
+      <c r="E185" t="n">
         <v>241050480</v>
       </c>
     </row>
@@ -3768,15 +4325,18 @@
           <t>TUPY3</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B186" t="n">
+        <v>188</v>
+      </c>
+      <c r="C186" t="inlineStr">
         <is>
           <t>Tupy</t>
         </is>
       </c>
-      <c r="C186" t="n">
+      <c r="D186" t="n">
         <v>382700</v>
       </c>
-      <c r="D186" t="n">
+      <c r="E186" t="n">
         <v>2889404416</v>
       </c>
     </row>
@@ -3786,15 +4346,18 @@
           <t>LIGT3</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
+      <c r="B187" t="n">
+        <v>189</v>
+      </c>
+      <c r="C187" t="inlineStr">
         <is>
           <t>Light</t>
         </is>
       </c>
-      <c r="C187" t="n">
+      <c r="D187" t="n">
         <v>380200</v>
       </c>
-      <c r="D187" t="n">
+      <c r="E187" t="n">
         <v>2052594688</v>
       </c>
     </row>
@@ -3804,15 +4367,18 @@
           <t>BMGB4</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
+      <c r="B188" t="n">
+        <v>190</v>
+      </c>
+      <c r="C188" t="inlineStr">
         <is>
           <t>Banco BMG</t>
         </is>
       </c>
-      <c r="C188" t="n">
+      <c r="D188" t="n">
         <v>367100</v>
       </c>
-      <c r="D188" t="n">
+      <c r="E188" t="n">
         <v>2209949184</v>
       </c>
     </row>
@@ -3822,15 +4388,18 @@
           <t>LOGG3</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr">
+      <c r="B189" t="n">
+        <v>191</v>
+      </c>
+      <c r="C189" t="inlineStr">
         <is>
           <t>LOG CP</t>
         </is>
       </c>
-      <c r="C189" t="n">
+      <c r="D189" t="n">
         <v>359900</v>
       </c>
-      <c r="D189" t="n">
+      <c r="E189" t="n">
         <v>1570337280</v>
       </c>
     </row>
@@ -3840,15 +4409,18 @@
           <t>CMIG3</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr">
+      <c r="B190" t="n">
+        <v>192</v>
+      </c>
+      <c r="C190" t="inlineStr">
         <is>
           <t>Cemig</t>
         </is>
       </c>
-      <c r="C190" t="n">
+      <c r="D190" t="n">
         <v>338200</v>
       </c>
-      <c r="D190" t="n">
+      <c r="E190" t="n">
         <v>35083681792</v>
       </c>
     </row>
@@ -3858,15 +4430,18 @@
           <t>FRAS3</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
+      <c r="B191" t="n">
+        <v>193</v>
+      </c>
+      <c r="C191" t="inlineStr">
         <is>
           <t>Fras-le</t>
         </is>
       </c>
-      <c r="C191" t="n">
+      <c r="D191" t="n">
         <v>333300</v>
       </c>
-      <c r="D191" t="n">
+      <c r="E191" t="n">
         <v>7043881984</v>
       </c>
     </row>
@@ -3876,15 +4451,18 @@
           <t>KLBN3</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="B192" t="n">
+        <v>194</v>
+      </c>
+      <c r="C192" t="inlineStr">
         <is>
           <t>Klabin</t>
         </is>
       </c>
-      <c r="C192" t="n">
+      <c r="D192" t="n">
         <v>332300</v>
       </c>
-      <c r="D192" t="n">
+      <c r="E192" t="n">
         <v>23981590528</v>
       </c>
     </row>
@@ -3894,15 +4472,18 @@
           <t>BLAU3</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="B193" t="n">
+        <v>195</v>
+      </c>
+      <c r="C193" t="inlineStr">
         <is>
           <t>Blau Farmacêutica</t>
         </is>
       </c>
-      <c r="C193" t="n">
+      <c r="D193" t="n">
         <v>318400</v>
       </c>
-      <c r="D193" t="n">
+      <c r="E193" t="n">
         <v>2077090688</v>
       </c>
     </row>
@@ -3912,15 +4493,18 @@
           <t>FIQE3</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
+      <c r="B194" t="n">
+        <v>196</v>
+      </c>
+      <c r="C194" t="inlineStr">
         <is>
           <t>Unifique</t>
         </is>
       </c>
-      <c r="C194" t="n">
+      <c r="D194" t="n">
         <v>316400</v>
       </c>
-      <c r="D194" t="n">
+      <c r="E194" t="n">
         <v>1228613888</v>
       </c>
     </row>
@@ -3930,15 +4514,18 @@
           <t>RANI3</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
+      <c r="B195" t="n">
+        <v>197</v>
+      </c>
+      <c r="C195" t="inlineStr">
         <is>
           <t>Irani</t>
         </is>
       </c>
-      <c r="C195" t="n">
+      <c r="D195" t="n">
         <v>312500</v>
       </c>
-      <c r="D195" t="n">
+      <c r="E195" t="n">
         <v>1702950912</v>
       </c>
     </row>
@@ -3948,15 +4535,18 @@
           <t>SOJA3</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
+      <c r="B196" t="n">
+        <v>198</v>
+      </c>
+      <c r="C196" t="inlineStr">
         <is>
           <t>Boa Safra Sementes</t>
         </is>
       </c>
-      <c r="C196" t="n">
+      <c r="D196" t="n">
         <v>304300</v>
       </c>
-      <c r="D196" t="n">
+      <c r="E196" t="n">
         <v>1388246400</v>
       </c>
     </row>
@@ -3966,15 +4556,18 @@
           <t>USIM3</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
+      <c r="B197" t="n">
+        <v>199</v>
+      </c>
+      <c r="C197" t="inlineStr">
         <is>
           <t>Usiminas</t>
         </is>
       </c>
-      <c r="C197" t="n">
+      <c r="D197" t="n">
         <v>298500</v>
       </c>
-      <c r="D197" t="n">
+      <c r="E197" t="n">
         <v>7217203200</v>
       </c>
     </row>
@@ -3984,15 +4577,18 @@
           <t>LEVE3</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr">
+      <c r="B198" t="n">
+        <v>200</v>
+      </c>
+      <c r="C198" t="inlineStr">
         <is>
           <t>Mahle Metal Leve</t>
         </is>
       </c>
-      <c r="C198" t="n">
+      <c r="D198" t="n">
         <v>285600</v>
       </c>
-      <c r="D198" t="n">
+      <c r="E198" t="n">
         <v>4087856384</v>
       </c>
     </row>
@@ -4002,15 +4598,18 @@
           <t>VITT3</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="B199" t="n">
+        <v>201</v>
+      </c>
+      <c r="C199" t="inlineStr">
         <is>
           <t>Vittia</t>
         </is>
       </c>
-      <c r="C199" t="n">
+      <c r="D199" t="n">
         <v>258000</v>
       </c>
-      <c r="D199" t="n">
+      <c r="E199" t="n">
         <v>790632832</v>
       </c>
     </row>
@@ -4020,15 +4619,18 @@
           <t>PNVL3</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
+      <c r="B200" t="n">
+        <v>202</v>
+      </c>
+      <c r="C200" t="inlineStr">
         <is>
           <t>Dimed</t>
         </is>
       </c>
-      <c r="C200" t="n">
+      <c r="D200" t="n">
         <v>257400</v>
       </c>
-      <c r="D200" t="n">
+      <c r="E200" t="n">
         <v>1258770432</v>
       </c>
     </row>
@@ -4038,15 +4640,18 @@
           <t>SANB4</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
+      <c r="B201" t="n">
+        <v>203</v>
+      </c>
+      <c r="C201" t="inlineStr">
         <is>
           <t>Banco Santander</t>
         </is>
       </c>
-      <c r="C201" t="n">
+      <c r="D201" t="n">
         <v>244900</v>
       </c>
-      <c r="D201" t="n">
+      <c r="E201" t="n">
         <v>97784553472</v>
       </c>
     </row>
@@ -4056,15 +4661,18 @@
           <t>ELMD3</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
+      <c r="B202" t="n">
+        <v>204</v>
+      </c>
+      <c r="C202" t="inlineStr">
         <is>
           <t>Eletromidia</t>
         </is>
       </c>
-      <c r="C202" t="n">
+      <c r="D202" t="n">
         <v>238600</v>
       </c>
-      <c r="D202" t="n">
+      <c r="E202" t="n">
         <v>4165577984</v>
       </c>
     </row>
@@ -4074,15 +4682,18 @@
           <t>SANB3</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
+      <c r="B203" t="n">
+        <v>205</v>
+      </c>
+      <c r="C203" t="inlineStr">
         <is>
           <t>Banco Santander</t>
         </is>
       </c>
-      <c r="C203" t="n">
+      <c r="D203" t="n">
         <v>230600</v>
       </c>
-      <c r="D203" t="n">
+      <c r="E203" t="n">
         <v>97784496128</v>
       </c>
     </row>
@@ -4092,15 +4703,18 @@
           <t>POMO3</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
+      <c r="B204" t="n">
+        <v>206</v>
+      </c>
+      <c r="C204" t="inlineStr">
         <is>
           <t>Marcopolo</t>
         </is>
       </c>
-      <c r="C204" t="n">
+      <c r="D204" t="n">
         <v>227300</v>
       </c>
-      <c r="D204" t="n">
+      <c r="E204" t="n">
         <v>7423163904</v>
       </c>
     </row>
@@ -4110,15 +4724,18 @@
           <t>TASA4</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
+      <c r="B205" t="n">
+        <v>207</v>
+      </c>
+      <c r="C205" t="inlineStr">
         <is>
           <t>Taurus</t>
         </is>
       </c>
-      <c r="C205" t="n">
+      <c r="D205" t="n">
         <v>221600</v>
       </c>
-      <c r="D205" t="n">
+      <c r="E205" t="n">
         <v>1017344704</v>
       </c>
     </row>
@@ -4128,15 +4745,18 @@
           <t>CAMB3</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="B206" t="n">
+        <v>208</v>
+      </c>
+      <c r="C206" t="inlineStr">
         <is>
           <t>Cambuci</t>
         </is>
       </c>
-      <c r="C206" t="n">
+      <c r="D206" t="n">
         <v>217600</v>
       </c>
-      <c r="D206" t="n">
+      <c r="E206" t="n">
         <v>431298080</v>
       </c>
     </row>
@@ -4146,15 +4766,18 @@
           <t>BOBR4</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B207" t="n">
+        <v>210</v>
+      </c>
+      <c r="C207" t="inlineStr">
         <is>
           <t>Bombril</t>
         </is>
       </c>
-      <c r="C207" t="n">
+      <c r="D207" t="n">
         <v>204400</v>
       </c>
-      <c r="D207" t="n">
+      <c r="E207" t="n">
         <v>213835568</v>
       </c>
     </row>
@@ -4164,15 +4787,18 @@
           <t>BMOB3</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B208" t="n">
+        <v>211</v>
+      </c>
+      <c r="C208" t="inlineStr">
         <is>
           <t>Bemobi</t>
         </is>
       </c>
-      <c r="C208" t="n">
+      <c r="D208" t="n">
         <v>197700</v>
       </c>
-      <c r="D208" t="n">
+      <c r="E208" t="n">
         <v>1263228032</v>
       </c>
     </row>
@@ -4182,15 +4808,18 @@
           <t>TAEE4</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B209" t="n">
+        <v>212</v>
+      </c>
+      <c r="C209" t="inlineStr">
         <is>
           <t>Taesa</t>
         </is>
       </c>
-      <c r="C209" t="n">
+      <c r="D209" t="n">
         <v>187400</v>
       </c>
-      <c r="D209" t="n">
+      <c r="E209" t="n">
         <v>11730226176</v>
       </c>
     </row>
@@ -4200,15 +4829,18 @@
           <t>ROMI3</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="B210" t="n">
+        <v>213</v>
+      </c>
+      <c r="C210" t="inlineStr">
         <is>
           <t>Indústrias ROMI</t>
         </is>
       </c>
-      <c r="C210" t="n">
+      <c r="D210" t="n">
         <v>183900</v>
       </c>
-      <c r="D210" t="n">
+      <c r="E210" t="n">
         <v>900960704</v>
       </c>
     </row>
@@ -4218,15 +4850,18 @@
           <t>TGMA3</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="B211" t="n">
+        <v>214</v>
+      </c>
+      <c r="C211" t="inlineStr">
         <is>
           <t>Tegma</t>
         </is>
       </c>
-      <c r="C211" t="n">
+      <c r="D211" t="n">
         <v>175800</v>
       </c>
-      <c r="D211" t="n">
+      <c r="E211" t="n">
         <v>2274194944</v>
       </c>
     </row>
@@ -4236,15 +4871,18 @@
           <t>COCE5</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="B212" t="n">
+        <v>215</v>
+      </c>
+      <c r="C212" t="inlineStr">
         <is>
           <t>Coelce</t>
         </is>
       </c>
-      <c r="C212" t="n">
+      <c r="D212" t="n">
         <v>171400</v>
       </c>
-      <c r="D212" t="n">
+      <c r="E212" t="n">
         <v>1882730880</v>
       </c>
     </row>
@@ -4254,15 +4892,18 @@
           <t>TPIS3</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B213" t="n">
+        <v>217</v>
+      </c>
+      <c r="C213" t="inlineStr">
         <is>
           <t>Triunfo</t>
         </is>
       </c>
-      <c r="C213" t="n">
+      <c r="D213" t="n">
         <v>167200</v>
       </c>
-      <c r="D213" t="n">
+      <c r="E213" t="n">
         <v>189121984</v>
       </c>
     </row>
@@ -4272,15 +4913,18 @@
           <t>FICT3</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
+      <c r="B214" t="n">
+        <v>218</v>
+      </c>
+      <c r="C214" t="inlineStr">
         <is>
           <t>Fictor Alimentos</t>
         </is>
       </c>
-      <c r="C214" t="n">
+      <c r="D214" t="n">
         <v>162800</v>
       </c>
-      <c r="D214" t="n">
+      <c r="E214" t="n">
         <v>92296472</v>
       </c>
     </row>
@@ -4290,15 +4934,18 @@
           <t>AMBP3</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
+      <c r="B215" t="n">
+        <v>219</v>
+      </c>
+      <c r="C215" t="inlineStr">
         <is>
           <t>Ambipar</t>
         </is>
       </c>
-      <c r="C215" t="n">
+      <c r="D215" t="n">
         <v>158100</v>
       </c>
-      <c r="D215" t="n">
+      <c r="E215" t="n">
         <v>21726478336</v>
       </c>
     </row>
@@ -4308,15 +4955,18 @@
           <t>AGRO3</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
+      <c r="B216" t="n">
+        <v>220</v>
+      </c>
+      <c r="C216" t="inlineStr">
         <is>
           <t>BrasilAgro</t>
         </is>
       </c>
-      <c r="C216" t="n">
+      <c r="D216" t="n">
         <v>155800</v>
       </c>
-      <c r="D216" t="n">
+      <c r="E216" t="n">
         <v>2132767872</v>
       </c>
     </row>
@@ -4326,15 +4976,18 @@
           <t>AGXY3</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
+      <c r="B217" t="n">
+        <v>221</v>
+      </c>
+      <c r="C217" t="inlineStr">
         <is>
           <t>AgroGalaxy</t>
         </is>
       </c>
-      <c r="C217" t="n">
+      <c r="D217" t="n">
         <v>152600</v>
       </c>
-      <c r="D217" t="n">
+      <c r="E217" t="n">
         <v>128085480</v>
       </c>
     </row>
@@ -4344,15 +4997,18 @@
           <t>ITSA3</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="B218" t="n">
+        <v>222</v>
+      </c>
+      <c r="C218" t="inlineStr">
         <is>
           <t>Itaúsa</t>
         </is>
       </c>
-      <c r="C218" t="n">
+      <c r="D218" t="n">
         <v>137500</v>
       </c>
-      <c r="D218" t="n">
+      <c r="E218" t="n">
         <v>102134398976</v>
       </c>
     </row>
@@ -4362,15 +5018,18 @@
           <t>SAPR3</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B219" t="n">
+        <v>223</v>
+      </c>
+      <c r="C219" t="inlineStr">
         <is>
           <t>Sanepar</t>
         </is>
       </c>
-      <c r="C219" t="n">
+      <c r="D219" t="n">
         <v>122300</v>
       </c>
-      <c r="D219" t="n">
+      <c r="E219" t="n">
         <v>8442608640</v>
       </c>
     </row>
@@ -4380,15 +5039,18 @@
           <t>PINE4</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="B220" t="n">
+        <v>224</v>
+      </c>
+      <c r="C220" t="inlineStr">
         <is>
           <t>Banco Pine</t>
         </is>
       </c>
-      <c r="C220" t="n">
+      <c r="D220" t="n">
         <v>120500</v>
       </c>
-      <c r="D220" t="n">
+      <c r="E220" t="n">
         <v>1020324544</v>
       </c>
     </row>
@@ -4398,15 +5060,18 @@
           <t>SCAR3</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B221" t="n">
+        <v>225</v>
+      </c>
+      <c r="C221" t="inlineStr">
         <is>
           <t>São Carlos</t>
         </is>
       </c>
-      <c r="C221" t="n">
+      <c r="D221" t="n">
         <v>113700</v>
       </c>
-      <c r="D221" t="n">
+      <c r="E221" t="n">
         <v>1030081984</v>
       </c>
     </row>
@@ -4416,15 +5081,18 @@
           <t>PFRM3</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B222" t="n">
+        <v>226</v>
+      </c>
+      <c r="C222" t="inlineStr">
         <is>
           <t>Profarma</t>
         </is>
       </c>
-      <c r="C222" t="n">
+      <c r="D222" t="n">
         <v>110200</v>
       </c>
-      <c r="D222" t="n">
+      <c r="E222" t="n">
         <v>899964736</v>
       </c>
     </row>
@@ -4434,15 +5102,18 @@
           <t>LPSB3</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B223" t="n">
+        <v>227</v>
+      </c>
+      <c r="C223" t="inlineStr">
         <is>
           <t>Lopes</t>
         </is>
       </c>
-      <c r="C223" t="n">
+      <c r="D223" t="n">
         <v>108800</v>
       </c>
-      <c r="D223" t="n">
+      <c r="E223" t="n">
         <v>182593040</v>
       </c>
     </row>
@@ -4452,15 +5123,18 @@
           <t>PMAM3</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
+      <c r="B224" t="n">
+        <v>228</v>
+      </c>
+      <c r="C224" t="inlineStr">
         <is>
           <t>Paranapanema</t>
         </is>
       </c>
-      <c r="C224" t="n">
+      <c r="D224" t="n">
         <v>107400</v>
       </c>
-      <c r="D224" t="n">
+      <c r="E224" t="n">
         <v>86603664</v>
       </c>
     </row>
@@ -4470,15 +5144,18 @@
           <t>RNEW4</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
+      <c r="B225" t="n">
+        <v>230</v>
+      </c>
+      <c r="C225" t="inlineStr">
         <is>
           <t>Renova Energia</t>
         </is>
       </c>
-      <c r="C225" t="n">
+      <c r="D225" t="n">
         <v>96900</v>
       </c>
-      <c r="D225" t="n">
+      <c r="E225" t="n">
         <v>215803504</v>
       </c>
     </row>
@@ -4488,15 +5165,18 @@
           <t>TAEE3</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
+      <c r="B226" t="n">
+        <v>231</v>
+      </c>
+      <c r="C226" t="inlineStr">
         <is>
           <t>Taesa</t>
         </is>
       </c>
-      <c r="C226" t="n">
+      <c r="D226" t="n">
         <v>89800</v>
       </c>
-      <c r="D226" t="n">
+      <c r="E226" t="n">
         <v>11730226176</v>
       </c>
     </row>
@@ -4506,15 +5186,18 @@
           <t>UCAS3</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="B227" t="n">
+        <v>232</v>
+      </c>
+      <c r="C227" t="inlineStr">
         <is>
           <t>Unicasa</t>
         </is>
       </c>
-      <c r="C227" t="n">
+      <c r="D227" t="n">
         <v>88900</v>
       </c>
-      <c r="D227" t="n">
+      <c r="E227" t="n">
         <v>101773056</v>
       </c>
     </row>
@@ -4524,15 +5207,18 @@
           <t>ETER3</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
+      <c r="B228" t="n">
+        <v>233</v>
+      </c>
+      <c r="C228" t="inlineStr">
         <is>
           <t>Eternit</t>
         </is>
       </c>
-      <c r="C228" t="n">
+      <c r="D228" t="n">
         <v>74200</v>
       </c>
-      <c r="D228" t="n">
+      <c r="E228" t="n">
         <v>307633984</v>
       </c>
     </row>
@@ -4542,15 +5228,18 @@
           <t>EALT4</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
+      <c r="B229" t="n">
+        <v>234</v>
+      </c>
+      <c r="C229" t="inlineStr">
         <is>
           <t>Electro Aço Altona</t>
         </is>
       </c>
-      <c r="C229" t="n">
+      <c r="D229" t="n">
         <v>73900</v>
       </c>
-      <c r="D229" t="n">
+      <c r="E229" t="n">
         <v>301080000</v>
       </c>
     </row>
@@ -4560,15 +5249,18 @@
           <t>RNEW3</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
+      <c r="B230" t="n">
+        <v>235</v>
+      </c>
+      <c r="C230" t="inlineStr">
         <is>
           <t>Renova Energia</t>
         </is>
       </c>
-      <c r="C230" t="n">
+      <c r="D230" t="n">
         <v>72100</v>
       </c>
-      <c r="D230" t="n">
+      <c r="E230" t="n">
         <v>215803248</v>
       </c>
     </row>
@@ -4578,15 +5270,18 @@
           <t>LUPA3</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
+      <c r="B231" t="n">
+        <v>236</v>
+      </c>
+      <c r="C231" t="inlineStr">
         <is>
           <t>Lupatech</t>
         </is>
       </c>
-      <c r="C231" t="n">
+      <c r="D231" t="n">
         <v>71400</v>
       </c>
-      <c r="D231" t="n">
+      <c r="E231" t="n">
         <v>50989040</v>
       </c>
     </row>
@@ -4596,15 +5291,18 @@
           <t>DEXP3</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
+      <c r="B232" t="n">
+        <v>237</v>
+      </c>
+      <c r="C232" t="inlineStr">
         <is>
           <t>Dexxos</t>
         </is>
       </c>
-      <c r="C232" t="n">
+      <c r="D232" t="n">
         <v>66300</v>
       </c>
-      <c r="D232" t="n">
+      <c r="E232" t="n">
         <v>883818560</v>
       </c>
     </row>
@@ -4614,15 +5312,18 @@
           <t>BRAP3</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr">
+      <c r="B233" t="n">
+        <v>238</v>
+      </c>
+      <c r="C233" t="inlineStr">
         <is>
           <t>Bradespar</t>
         </is>
       </c>
-      <c r="C233" t="n">
+      <c r="D233" t="n">
         <v>62700</v>
       </c>
-      <c r="D233" t="n">
+      <c r="E233" t="n">
         <v>6669444096</v>
       </c>
     </row>
@@ -4632,15 +5333,18 @@
           <t>IGTI3</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
+      <c r="B234" t="n">
+        <v>239</v>
+      </c>
+      <c r="C234" t="inlineStr">
         <is>
           <t>Jereissati Participações</t>
         </is>
       </c>
-      <c r="C234" t="n">
+      <c r="D234" t="n">
         <v>62100</v>
       </c>
-      <c r="D234" t="n">
+      <c r="E234" t="n">
         <v>5093064192</v>
       </c>
     </row>
@@ -4650,15 +5354,18 @@
           <t>TECN3</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B235" t="n">
+        <v>242</v>
+      </c>
+      <c r="C235" t="inlineStr">
         <is>
           <t>Technos</t>
         </is>
       </c>
-      <c r="C235" t="n">
+      <c r="D235" t="n">
         <v>52700</v>
       </c>
-      <c r="D235" t="n">
+      <c r="E235" t="n">
         <v>333557216</v>
       </c>
     </row>
@@ -4668,15 +5375,18 @@
           <t>ALPK3</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
+      <c r="B236" t="n">
+        <v>243</v>
+      </c>
+      <c r="C236" t="inlineStr">
         <is>
           <t>Estapar</t>
         </is>
       </c>
-      <c r="C236" t="n">
+      <c r="D236" t="n">
         <v>49600</v>
       </c>
-      <c r="D236" t="n">
+      <c r="E236" t="n">
         <v>625248768</v>
       </c>
     </row>
@@ -4686,15 +5396,18 @@
           <t>CSUD3</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
+      <c r="B237" t="n">
+        <v>245</v>
+      </c>
+      <c r="C237" t="inlineStr">
         <is>
           <t>CSU Cardsystem</t>
         </is>
       </c>
-      <c r="C237" t="n">
+      <c r="D237" t="n">
         <v>47600</v>
       </c>
-      <c r="D237" t="n">
+      <c r="E237" t="n">
         <v>677006720</v>
       </c>
     </row>
@@ -4704,15 +5417,18 @@
           <t>DMVF3</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
+      <c r="B238" t="n">
+        <v>246</v>
+      </c>
+      <c r="C238" t="inlineStr">
         <is>
           <t>D1000 Varejo Farma</t>
         </is>
       </c>
-      <c r="C238" t="n">
+      <c r="D238" t="n">
         <v>47300</v>
       </c>
-      <c r="D238" t="n">
+      <c r="E238" t="n">
         <v>303616800</v>
       </c>
     </row>
@@ -4722,15 +5438,18 @@
           <t>LOGN3</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
+      <c r="B239" t="n">
+        <v>247</v>
+      </c>
+      <c r="C239" t="inlineStr">
         <is>
           <t>Log-In</t>
         </is>
       </c>
-      <c r="C239" t="n">
+      <c r="D239" t="n">
         <v>41100</v>
       </c>
-      <c r="D239" t="n">
+      <c r="E239" t="n">
         <v>2280891904</v>
       </c>
     </row>
@@ -4740,15 +5459,18 @@
           <t>TCSA3</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
+      <c r="B240" t="n">
+        <v>248</v>
+      </c>
+      <c r="C240" t="inlineStr">
         <is>
           <t>Tecnisa</t>
         </is>
       </c>
-      <c r="C240" t="n">
+      <c r="D240" t="n">
         <v>39100</v>
       </c>
-      <c r="D240" t="n">
+      <c r="E240" t="n">
         <v>106011656</v>
       </c>
     </row>
@@ -4758,15 +5480,18 @@
           <t>GOAU3</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
+      <c r="B241" t="n">
+        <v>249</v>
+      </c>
+      <c r="C241" t="inlineStr">
         <is>
           <t>Metalúrgica Gerdau</t>
         </is>
       </c>
-      <c r="C241" t="n">
+      <c r="D241" t="n">
         <v>38900</v>
       </c>
-      <c r="D241" t="n">
+      <c r="E241" t="n">
         <v>9424949248</v>
       </c>
     </row>
@@ -4776,15 +5501,18 @@
           <t>RSID3</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
+      <c r="B242" t="n">
+        <v>250</v>
+      </c>
+      <c r="C242" t="inlineStr">
         <is>
           <t>Rossi Residencial</t>
         </is>
       </c>
-      <c r="C242" t="n">
+      <c r="D242" t="n">
         <v>38700</v>
       </c>
-      <c r="D242" t="n">
+      <c r="E242" t="n">
         <v>57684308</v>
       </c>
     </row>
@@ -4794,15 +5522,18 @@
           <t>BIOM3</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
+      <c r="B243" t="n">
+        <v>251</v>
+      </c>
+      <c r="C243" t="inlineStr">
         <is>
           <t>Biomm</t>
         </is>
       </c>
-      <c r="C243" t="n">
+      <c r="D243" t="n">
         <v>38600</v>
       </c>
-      <c r="D243" t="n">
+      <c r="E243" t="n">
         <v>1291241472</v>
       </c>
     </row>
@@ -4812,15 +5543,18 @@
           <t>LVTC3</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
+      <c r="B244" t="n">
+        <v>253</v>
+      </c>
+      <c r="C244" t="inlineStr">
         <is>
           <t>WDC Networks</t>
         </is>
       </c>
-      <c r="C244" t="n">
+      <c r="D244" t="n">
         <v>26100</v>
       </c>
-      <c r="D244" t="n">
+      <c r="E244" t="n">
         <v>155480672</v>
       </c>
     </row>
@@ -4830,15 +5564,18 @@
           <t>ALPA3</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
+      <c r="B245" t="n">
+        <v>254</v>
+      </c>
+      <c r="C245" t="inlineStr">
         <is>
           <t>Alpargatas</t>
         </is>
       </c>
-      <c r="C245" t="n">
+      <c r="D245" t="n">
         <v>25500</v>
       </c>
-      <c r="D245" t="n">
+      <c r="E245" t="n">
         <v>4706682368</v>
       </c>
     </row>
@@ -4848,15 +5585,18 @@
           <t>INEP3</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
+      <c r="B246" t="n">
+        <v>255</v>
+      </c>
+      <c r="C246" t="inlineStr">
         <is>
           <t>Inepar</t>
         </is>
       </c>
-      <c r="C246" t="n">
+      <c r="D246" t="n">
         <v>25400</v>
       </c>
-      <c r="D246" t="n">
+      <c r="E246" t="n">
         <v>65073812</v>
       </c>
     </row>
@@ -4866,15 +5606,18 @@
           <t>ENGI4</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
+      <c r="B247" t="n">
+        <v>256</v>
+      </c>
+      <c r="C247" t="inlineStr">
         <is>
           <t>Energisa</t>
         </is>
       </c>
-      <c r="C247" t="n">
+      <c r="D247" t="n">
         <v>24400</v>
       </c>
-      <c r="D247" t="n">
+      <c r="E247" t="n">
         <v>20799023104</v>
       </c>
     </row>
@@ -4884,15 +5627,18 @@
           <t>ALLD3</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
+      <c r="B248" t="n">
+        <v>257</v>
+      </c>
+      <c r="C248" t="inlineStr">
         <is>
           <t>Allied</t>
         </is>
       </c>
-      <c r="C248" t="n">
+      <c r="D248" t="n">
         <v>23200</v>
       </c>
-      <c r="D248" t="n">
+      <c r="E248" t="n">
         <v>663115968</v>
       </c>
     </row>
@@ -4902,15 +5648,18 @@
           <t>KRSA3</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr">
+      <c r="B249" t="n">
+        <v>258</v>
+      </c>
+      <c r="C249" t="inlineStr">
         <is>
           <t>Kora Saúde</t>
         </is>
       </c>
-      <c r="C249" t="n">
+      <c r="D249" t="n">
         <v>20700</v>
       </c>
-      <c r="D249" t="n">
+      <c r="E249" t="n">
         <v>674443776</v>
       </c>
     </row>

--- a/Bases/Lista de ações Tratada.xlsx
+++ b/Bases/Lista de ações Tratada.xlsx
@@ -8234,7 +8234,7 @@
         <v>0.16244721</v>
       </c>
       <c r="AE33">
-        <v>0.202009</v>
+        <v>0.235195</v>
       </c>
       <c r="AF33">
         <v>1745539200</v>
@@ -11897,10 +11897,10 @@
         <v>-0.35174745</v>
       </c>
       <c r="AE54">
-        <v>0.25</v>
+        <v>0.450164</v>
       </c>
       <c r="AF54">
-        <v>1723766400</v>
+        <v>1741305600</v>
       </c>
       <c r="AG54">
         <v>2.6875</v>
@@ -15560,7 +15560,7 @@
         <v>0.08237707599999999</v>
       </c>
       <c r="AE75">
-        <v>0.074072</v>
+        <v>0.074027</v>
       </c>
       <c r="AF75">
         <v>1744588800</v>
@@ -18609,10 +18609,10 @@
         <v>0.20395005</v>
       </c>
       <c r="AE92">
-        <v>0.156105</v>
+        <v>0.202583</v>
       </c>
       <c r="AF92">
-        <v>1727395200</v>
+        <v>1734566400</v>
       </c>
       <c r="AG92">
         <v>1.58333</v>
@@ -21831,10 +21831,10 @@
         <v>-0.11806595</v>
       </c>
       <c r="AE110">
-        <v>1.39228</v>
+        <v>0.153465</v>
       </c>
       <c r="AF110">
-        <v>1735776000</v>
+        <v>1717113600</v>
       </c>
       <c r="AG110">
         <v>2.66667</v>
@@ -22189,10 +22189,10 @@
         <v>0.09348202</v>
       </c>
       <c r="AE112">
-        <v>0.783358</v>
+        <v>1.610052</v>
       </c>
       <c r="AF112">
-        <v>1692316800</v>
+        <v>1745971200</v>
       </c>
       <c r="AG112">
         <v>2.72727</v>
@@ -23946,10 +23946,10 @@
         <v>0.37148666</v>
       </c>
       <c r="AE122">
-        <v>0.605805</v>
+        <v>0.421051</v>
       </c>
       <c r="AF122">
-        <v>1743379200</v>
+        <v>1735776000</v>
       </c>
       <c r="AG122">
         <v>1.63636</v>
@@ -24838,10 +24838,10 @@
         <v>-0.2983871</v>
       </c>
       <c r="AE127">
-        <v>0.274569</v>
+        <v>0.185884</v>
       </c>
       <c r="AF127">
-        <v>1741219200</v>
+        <v>1722556800</v>
       </c>
       <c r="AG127">
         <v>1.88889</v>
@@ -25202,7 +25202,7 @@
         <v>-0.24482208</v>
       </c>
       <c r="AE129">
-        <v>0.324923</v>
+        <v>0.093081</v>
       </c>
       <c r="AF129">
         <v>1744329600</v>
@@ -42963,10 +42963,10 @@
         <v>-0.6054945</v>
       </c>
       <c r="AE233">
-        <v>47.55625</v>
+        <v>510.689</v>
       </c>
       <c r="AF233">
-        <v>1207699200</v>
+        <v>1363910400</v>
       </c>
       <c r="AH233" t="s">
         <v>683</v>
@@ -45184,10 +45184,10 @@
         <v>-0.12364131</v>
       </c>
       <c r="AE247">
-        <v>0.212294</v>
+        <v>0.270746</v>
       </c>
       <c r="AF247">
-        <v>1699315200</v>
+        <v>1730246400</v>
       </c>
       <c r="AH247" t="s">
         <v>683</v>
@@ -45354,7 +45354,7 @@
         <v>0.08</v>
       </c>
       <c r="AF248">
-        <v>1744848000</v>
+        <v>1731888000</v>
       </c>
       <c r="AH248" t="s">
         <v>683</v>

--- a/Bases/Lista de ações Tratada.xlsx
+++ b/Bases/Lista de ações Tratada.xlsx
@@ -13341,7 +13341,7 @@
         <v>0.2260766</v>
       </c>
       <c r="AF60">
-        <v>0.213813</v>
+        <v>0.183644</v>
       </c>
       <c r="AG60">
         <v>1745539200</v>
@@ -30214,10 +30214,10 @@
         <v>0.3409648</v>
       </c>
       <c r="AF155">
-        <v>0.596564</v>
+        <v>0.65</v>
       </c>
       <c r="AG155">
-        <v>1747872000</v>
+        <v>1731456000</v>
       </c>
       <c r="AH155">
         <v>1.2</v>
@@ -33928,7 +33928,7 @@
         <v>0.5</v>
       </c>
       <c r="AF176">
-        <v>0.3</v>
+        <v>0.300639</v>
       </c>
       <c r="AG176">
         <v>1745798400</v>

--- a/Bases/Lista de ações Tratada.xlsx
+++ b/Bases/Lista de ações Tratada.xlsx
@@ -13341,7 +13341,7 @@
         <v>0.2260766</v>
       </c>
       <c r="AF60">
-        <v>0.183644</v>
+        <v>0.213813</v>
       </c>
       <c r="AG60">
         <v>1745539200</v>
@@ -23647,7 +23647,7 @@
         <v>-0.21875</v>
       </c>
       <c r="AF119">
-        <v>0.093081</v>
+        <v>0.324923</v>
       </c>
       <c r="AG119">
         <v>1744329600</v>
@@ -33561,7 +33561,7 @@
         <v>0.73131776</v>
       </c>
       <c r="AF174">
-        <v>0.204417</v>
+        <v>0.8221580000000001</v>
       </c>
       <c r="AG174">
         <v>1746144000</v>
@@ -33928,7 +33928,7 @@
         <v>0.5</v>
       </c>
       <c r="AF176">
-        <v>0.300639</v>
+        <v>0.3</v>
       </c>
       <c r="AG176">
         <v>1745798400</v>
